--- a/LED_template.xlsx
+++ b/LED_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="3"/>
+    <workbookView windowWidth="14400" windowHeight="12375" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="LED" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="157">
   <si>
     <t>宇视Unigulf系列LED显示系统报价清单</t>
   </si>
@@ -412,6 +412,9 @@
     <t>8路HDMI输入接口，最高输入分辨率1920x1200@60HZ</t>
   </si>
   <si>
+    <t>一、LED显示大屏</t>
+  </si>
+  <si>
     <t>HUWAILED_MINGCHENG</t>
   </si>
   <si>
@@ -424,6 +427,21 @@
     <t>HUWAILED_DANJIA</t>
   </si>
   <si>
+    <t>含1%备件</t>
+  </si>
+  <si>
+    <t>模组</t>
+  </si>
+  <si>
+    <t>备件</t>
+  </si>
+  <si>
+    <t>接收卡</t>
+  </si>
+  <si>
+    <t>电源</t>
+  </si>
+  <si>
     <t>箱体</t>
   </si>
   <si>
@@ -433,13 +451,22 @@
     <t>国优</t>
   </si>
   <si>
-    <t>整体包边及防水处理</t>
-  </si>
-  <si>
-    <t>箱体组装</t>
-  </si>
-  <si>
-    <t>工厂散件组装成屏 老化测试 整屏出货</t>
+    <t>含箱体组装及内部排线和电源线</t>
+  </si>
+  <si>
+    <t>处理器</t>
+  </si>
+  <si>
+    <t>同步or异步</t>
+  </si>
+  <si>
+    <t>软件</t>
+  </si>
+  <si>
+    <t>二、配电与散热系统</t>
+  </si>
+  <si>
+    <t>配电柜</t>
   </si>
   <si>
     <t>空调</t>
@@ -448,46 +475,40 @@
     <t>2.5P散热空调，20平方散热</t>
   </si>
   <si>
-    <t>空气干燥风机</t>
+    <t>关于空调：20平方以内可以不加空调，大于20平方需要加空调，每20增加一个2P空调。</t>
+  </si>
+  <si>
+    <t>风机</t>
   </si>
   <si>
     <t>排热 温湿度循环</t>
   </si>
   <si>
-    <t>排线及5V线材、220V线材</t>
-  </si>
-  <si>
-    <t>包括从接收卡到板子的定制长排线、开关电源到单元板的电源线、接收卡与接收卡之间的网线，开关电源与开关电源之间的电源线。</t>
-  </si>
-  <si>
-    <t>显示屏箱体拼装、安装调试及培训服务及一年售后服务</t>
+    <t>风扇</t>
+  </si>
+  <si>
+    <t>音响功放</t>
+  </si>
+  <si>
+    <t>150W功放+2条50W音柱</t>
+  </si>
+  <si>
+    <t>音响</t>
+  </si>
+  <si>
+    <t>三、结构设计与安装</t>
   </si>
   <si>
     <t>钢结构</t>
   </si>
   <si>
-    <t>采用Q235镀锌钢材焊接结构</t>
-  </si>
-  <si>
-    <t>脚手架吊车费用</t>
-  </si>
-  <si>
-    <t>运输费用</t>
-  </si>
-  <si>
-    <t>工厂到现场的运输物流费</t>
-  </si>
-  <si>
-    <t>地基底座及安装</t>
-  </si>
-  <si>
-    <t>钢材，焊接和切割，固定安装, 深度整体600MM，不锈钢普通包边处理，含备板封板，双立柱，离地2米 混凝土浇筑</t>
-  </si>
-  <si>
     <t>国产</t>
   </si>
   <si>
-    <t>如果壁装就不需要</t>
+    <t>结构</t>
+  </si>
+  <si>
+    <t>安装</t>
   </si>
 </sst>
 </file>
@@ -563,14 +584,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1630,7 +1651,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1709,6 +1730,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1754,80 +1778,83 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3280,7 +3307,7 @@
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
-      <c r="J1" s="39"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A2" s="11"/>
@@ -3307,7 +3334,7 @@
       <c r="I2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="40"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A3" s="18"/>
@@ -3334,7 +3361,7 @@
       <c r="I3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="41"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A4" s="18"/>
@@ -3360,7 +3387,7 @@
       <c r="I4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -3390,7 +3417,7 @@
       <c r="I5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="44" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3406,7 +3433,7 @@
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="44"/>
+      <c r="J6" s="45"/>
     </row>
     <row r="7" ht="43" customHeight="1" spans="1:10">
       <c r="A7" s="24">
@@ -3437,7 +3464,7 @@
         <f t="shared" ref="I7:I14" si="0">F7*H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J7" s="45"/>
+      <c r="J7" s="71"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:10">
       <c r="A8" s="24">
@@ -3452,7 +3479,7 @@
       <c r="D8" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="31" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="28" t="s">
@@ -3468,7 +3495,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J8" s="45"/>
+      <c r="J8" s="71"/>
     </row>
     <row r="9" ht="57" customHeight="1" spans="1:10">
       <c r="A9" s="24">
@@ -3499,7 +3526,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J9" s="46"/>
+      <c r="J9" s="47"/>
     </row>
     <row r="10" ht="42.75" spans="1:10">
       <c r="A10" s="24">
@@ -3530,7 +3557,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="47"/>
+      <c r="J10" s="48"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="42.75" spans="1:10">
       <c r="A11" s="24">
@@ -3561,7 +3588,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="48"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="57" spans="1:10">
       <c r="A12" s="24">
@@ -3592,7 +3619,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="49" t="s">
+      <c r="J12" s="50" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3609,7 +3636,7 @@
       <c r="D13" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="31" t="s">
         <v>39</v>
       </c>
       <c r="F13" s="27">
@@ -3625,28 +3652,28 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J13" s="50"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" ht="43.5" spans="1:10">
       <c r="A14" s="24">
         <v>8</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="77" t="s">
+      <c r="D14" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="31" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="31" t="s">
         <v>34</v>
       </c>
       <c r="H14" s="28" t="s">
@@ -3656,36 +3683,36 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J14" s="71"/>
+      <c r="J14" s="73"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="78"/>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80" t="s">
+      <c r="A15" s="80"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="83" t="e">
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="85" t="e">
         <f>SUM(I7:I14)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J15" s="84"/>
+      <c r="J15" s="86"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="55"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4552,7 +4579,7 @@
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
-      <c r="J1" s="39"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A2" s="11"/>
@@ -4579,7 +4606,7 @@
       <c r="I2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="40"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A3" s="18"/>
@@ -4606,7 +4633,7 @@
       <c r="I3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="41"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A4" s="18"/>
@@ -4632,7 +4659,7 @@
       <c r="I4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -4662,7 +4689,7 @@
       <c r="I5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="44" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4678,7 +4705,7 @@
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="44"/>
+      <c r="J6" s="45"/>
     </row>
     <row r="7" ht="43" customHeight="1" spans="1:10">
       <c r="A7" s="24">
@@ -4709,7 +4736,7 @@
         <f t="shared" ref="I7:I17" si="0">F7*H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J7" s="45"/>
+      <c r="J7" s="71"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:10">
       <c r="A8" s="24">
@@ -4724,7 +4751,7 @@
       <c r="D8" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="31" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="28" t="s">
@@ -4740,7 +4767,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J8" s="45"/>
+      <c r="J8" s="71"/>
     </row>
     <row r="9" ht="57" customHeight="1" spans="1:10">
       <c r="A9" s="24">
@@ -4771,7 +4798,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J9" s="46"/>
+      <c r="J9" s="47"/>
     </row>
     <row r="10" ht="42.75" spans="1:10">
       <c r="A10" s="24">
@@ -4802,7 +4829,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="47"/>
+      <c r="J10" s="48"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="42.75" spans="1:10">
       <c r="A11" s="24">
@@ -4833,28 +4860,28 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="48"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="28.5" spans="1:10">
       <c r="A12" s="24">
         <v>6</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="75" t="s">
+      <c r="C12" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="77">
         <v>1</v>
       </c>
-      <c r="G12" s="75" t="s">
+      <c r="G12" s="77" t="s">
         <v>51</v>
       </c>
       <c r="H12" s="28" t="s">
@@ -4864,28 +4891,28 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J12" s="48"/>
+      <c r="J12" s="49"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="57" spans="1:10">
       <c r="A13" s="24">
         <v>7</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="76" t="s">
+      <c r="D13" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="75" t="s">
+      <c r="G13" s="77" t="s">
         <v>45</v>
       </c>
       <c r="H13" s="28" t="s">
@@ -4895,28 +4922,28 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J13" s="48"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="71.25" spans="1:10">
       <c r="A14" s="24">
         <v>8</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="75" t="s">
+      <c r="G14" s="77" t="s">
         <v>45</v>
       </c>
       <c r="H14" s="28" t="s">
@@ -4926,7 +4953,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J14" s="48"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="57" spans="1:10">
       <c r="A15" s="24">
@@ -4957,7 +4984,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="49" t="s">
+      <c r="J15" s="50" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4974,7 +5001,7 @@
       <c r="D16" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="31" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="27">
@@ -4990,28 +5017,28 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J16" s="50"/>
+      <c r="J16" s="51"/>
     </row>
     <row r="17" ht="43.5" spans="1:10">
       <c r="A17" s="24">
         <v>11</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="77" t="s">
+      <c r="D17" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="31" t="s">
         <v>39</v>
       </c>
       <c r="F17" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="30" t="s">
+      <c r="G17" s="31" t="s">
         <v>34</v>
       </c>
       <c r="H17" s="28" t="s">
@@ -5021,36 +5048,36 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J17" s="71"/>
+      <c r="J17" s="73"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="78"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80" t="s">
+      <c r="A18" s="80"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="83" t="e">
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85" t="e">
         <f>SUM(I7:I17)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="84"/>
+      <c r="J18" s="86"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="55"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5917,7 +5944,7 @@
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
-      <c r="J1" s="39"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A2" s="11"/>
@@ -5944,7 +5971,7 @@
       <c r="I2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="40"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A3" s="18"/>
@@ -5971,7 +5998,7 @@
       <c r="I3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="41"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A4" s="18"/>
@@ -5997,7 +6024,7 @@
       <c r="I4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -6027,23 +6054,23 @@
       <c r="I5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="44" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="69"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="70"/>
     </row>
     <row r="7" ht="119" customHeight="1" spans="1:10">
       <c r="A7" s="24">
@@ -6074,21 +6101,21 @@
         <f>F7*H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J7" s="45"/>
+      <c r="J7" s="71"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="69"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="70"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="42.75" spans="1:10">
       <c r="A9" s="24">
@@ -6119,7 +6146,7 @@
         <f>F9*H9</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="57" spans="1:10">
       <c r="A10" s="24">
@@ -6150,23 +6177,23 @@
         <f>F10*H10</f>
         <v>0</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="J10" s="50" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="69"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="70"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A12" s="24">
@@ -6175,10 +6202,10 @@
       <c r="B12" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="61" t="s">
+      <c r="D12" s="62" t="s">
         <v>94</v>
       </c>
       <c r="E12" s="27" t="s">
@@ -6197,7 +6224,7 @@
         <f t="shared" ref="I12:I14" si="0">F12*H12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="70" t="s">
+      <c r="J12" s="72" t="s">
         <v>95</v>
       </c>
     </row>
@@ -6230,7 +6257,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J13" s="50"/>
+      <c r="J13" s="51"/>
       <c r="XEK13" s="7"/>
       <c r="XEL13" s="7"/>
       <c r="XEM13" s="7"/>
@@ -6248,16 +6275,16 @@
       <c r="XEY13" s="7"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A14" s="62">
+      <c r="A14" s="63">
         <v>10</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="61" t="s">
+      <c r="D14" s="62" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="27" t="s">
@@ -6276,21 +6303,21 @@
         <f t="shared" si="0"/>
         <v>1450</v>
       </c>
-      <c r="J14" s="70"/>
+      <c r="J14" s="72"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="69"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="70"/>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:10">
       <c r="A16" s="24">
@@ -6299,10 +6326,10 @@
       <c r="B16" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="62" t="s">
         <v>101</v>
       </c>
       <c r="E16" s="27" t="s">
@@ -6321,7 +6348,7 @@
         <f t="shared" ref="I16:I20" si="1">F16*H16</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J16" s="71"/>
+      <c r="J16" s="73"/>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:10">
       <c r="A17" s="24">
@@ -6330,10 +6357,10 @@
       <c r="B17" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="61" t="s">
+      <c r="D17" s="62" t="s">
         <v>104</v>
       </c>
       <c r="E17" s="27" t="s">
@@ -6352,7 +6379,7 @@
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J17" s="71"/>
+      <c r="J17" s="73"/>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:10">
       <c r="A18" s="24">
@@ -6361,10 +6388,10 @@
       <c r="B18" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="61" t="s">
+      <c r="D18" s="62" t="s">
         <v>106</v>
       </c>
       <c r="E18" s="27" t="s">
@@ -6383,7 +6410,7 @@
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="71"/>
+      <c r="J18" s="73"/>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:10">
       <c r="A19" s="24">
@@ -6392,10 +6419,10 @@
       <c r="B19" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="61" t="s">
+      <c r="D19" s="62" t="s">
         <v>108</v>
       </c>
       <c r="E19" s="27" t="s">
@@ -6414,7 +6441,7 @@
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J19" s="71"/>
+      <c r="J19" s="73"/>
     </row>
     <row r="20" ht="16.5" spans="1:10">
       <c r="A20" s="24">
@@ -6423,10 +6450,10 @@
       <c r="B20" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="62" t="s">
         <v>110</v>
       </c>
       <c r="E20" s="27" t="s">
@@ -6445,70 +6472,70 @@
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J20" s="50"/>
+      <c r="J20" s="51"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="72" t="e">
+      <c r="B21" s="65"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="74" t="e">
         <f>SUM(I7:I14)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J21" s="70"/>
+      <c r="J21" s="72"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="72" t="e">
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="74" t="e">
         <f>SUM(I16:I20)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J22" s="70"/>
+      <c r="J22" s="72"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="73" t="e">
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="75" t="e">
         <f>SUM(I21:I22)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J23" s="74"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A24" s="37"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="55"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7384,7 +7411,7 @@
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
-      <c r="J1" s="39"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A2" s="11"/>
@@ -7411,7 +7438,7 @@
       <c r="I2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="40"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A3" s="18"/>
@@ -7438,7 +7465,7 @@
       <c r="I3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="41"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A4" s="18"/>
@@ -7464,7 +7491,7 @@
       <c r="I4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -7494,23 +7521,23 @@
       <c r="I5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="44" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="69"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="70"/>
     </row>
     <row r="7" ht="119" customHeight="1" spans="1:10">
       <c r="A7" s="24">
@@ -7541,21 +7568,21 @@
         <f t="shared" ref="I7:I14" si="0">F7*H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J7" s="45"/>
+      <c r="J7" s="71"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="69"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="70"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="42.75" spans="1:10">
       <c r="A9" s="24">
@@ -7586,7 +7613,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="127" customHeight="1" spans="1:10">
       <c r="A10" s="27">
@@ -7617,19 +7644,19 @@
         <f t="shared" si="0"/>
         <v>7480</v>
       </c>
-      <c r="J10" s="48"/>
+      <c r="J10" s="49"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="49.5" spans="1:10">
-      <c r="A11" s="59">
+      <c r="A11" s="60">
         <v>4</v>
       </c>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="60" t="s">
+      <c r="C11" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="61" t="s">
         <v>119</v>
       </c>
       <c r="E11" s="27" t="s">
@@ -7648,19 +7675,19 @@
         <f t="shared" si="0"/>
         <v>5520</v>
       </c>
-      <c r="J11" s="48"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:10">
-      <c r="A12" s="59">
+      <c r="A12" s="60">
         <v>5</v>
       </c>
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="60" t="s">
+      <c r="D12" s="61" t="s">
         <v>123</v>
       </c>
       <c r="E12" s="27" t="s">
@@ -7679,10 +7706,10 @@
         <f t="shared" si="0"/>
         <v>3220</v>
       </c>
-      <c r="J12" s="48"/>
+      <c r="J12" s="49"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="71.25" spans="1:10">
-      <c r="A13" s="59">
+      <c r="A13" s="60">
         <v>6</v>
       </c>
       <c r="B13" s="27" t="s">
@@ -7710,7 +7737,7 @@
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J13" s="48"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="57" spans="1:10">
       <c r="A14" s="24">
@@ -7741,23 +7768,23 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="49" t="s">
+      <c r="J14" s="50" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="69"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="70"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A16" s="24">
@@ -7769,7 +7796,7 @@
       <c r="C16" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="62" t="s">
         <v>94</v>
       </c>
       <c r="E16" s="27" t="s">
@@ -7788,7 +7815,7 @@
         <f t="shared" ref="I14:I18" si="1">F16*H16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="70" t="s">
+      <c r="J16" s="72" t="s">
         <v>95</v>
       </c>
     </row>
@@ -7821,7 +7848,7 @@
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J17" s="50"/>
+      <c r="J17" s="51"/>
       <c r="XEK17" s="7"/>
       <c r="XEL17" s="7"/>
       <c r="XEM17" s="7"/>
@@ -7839,7 +7866,7 @@
       <c r="XEY17" s="7"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A18" s="62">
+      <c r="A18" s="63">
         <v>10</v>
       </c>
       <c r="B18" s="17" t="s">
@@ -7848,7 +7875,7 @@
       <c r="C18" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="61" t="s">
+      <c r="D18" s="62" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="27" t="s">
@@ -7867,21 +7894,21 @@
         <f t="shared" si="1"/>
         <v>1450</v>
       </c>
-      <c r="J18" s="70"/>
+      <c r="J18" s="72"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="69"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="70"/>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:10">
       <c r="A20" s="24">
@@ -7893,7 +7920,7 @@
       <c r="C20" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="62" t="s">
         <v>101</v>
       </c>
       <c r="E20" s="27" t="s">
@@ -7912,7 +7939,7 @@
         <f t="shared" ref="I20:I24" si="2">F20*H20</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J20" s="71"/>
+      <c r="J20" s="73"/>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:10">
       <c r="A21" s="24">
@@ -7924,7 +7951,7 @@
       <c r="C21" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="61" t="s">
+      <c r="D21" s="62" t="s">
         <v>104</v>
       </c>
       <c r="E21" s="27" t="s">
@@ -7943,7 +7970,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J21" s="71"/>
+      <c r="J21" s="73"/>
     </row>
     <row r="22" s="2" customFormat="1" spans="1:10">
       <c r="A22" s="24">
@@ -7955,7 +7982,7 @@
       <c r="C22" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="61" t="s">
+      <c r="D22" s="62" t="s">
         <v>106</v>
       </c>
       <c r="E22" s="27" t="s">
@@ -7974,7 +8001,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J22" s="71"/>
+      <c r="J22" s="73"/>
     </row>
     <row r="23" s="2" customFormat="1" spans="1:10">
       <c r="A23" s="24">
@@ -7986,7 +8013,7 @@
       <c r="C23" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="61" t="s">
+      <c r="D23" s="62" t="s">
         <v>108</v>
       </c>
       <c r="E23" s="27" t="s">
@@ -8005,7 +8032,7 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J23" s="71"/>
+      <c r="J23" s="73"/>
     </row>
     <row r="24" ht="16.5" spans="1:10">
       <c r="A24" s="24">
@@ -8017,7 +8044,7 @@
       <c r="C24" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="62" t="s">
         <v>110</v>
       </c>
       <c r="E24" s="27" t="s">
@@ -8036,70 +8063,70 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J24" s="50"/>
+      <c r="J24" s="51"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="64"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="72" t="e">
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="74" t="e">
         <f>SUM(I7:I18)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J25" s="70"/>
+      <c r="J25" s="72"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A26" s="63" t="s">
+      <c r="A26" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="64"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="72" t="e">
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="74" t="e">
         <f>SUM(I20:I24)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J26" s="70"/>
+      <c r="J26" s="72"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="68"/>
-      <c r="I27" s="73" t="e">
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="75" t="e">
         <f>SUM(I25:I26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J27" s="74"/>
+      <c r="J27" s="76"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A28" s="37"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="55"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8126,7 +8153,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.25" style="3" customWidth="1"/>
@@ -8140,827 +8167,827 @@
     <col min="9" max="9" width="13.625" style="3" customWidth="1"/>
     <col min="10" max="10" width="15" style="3" customWidth="1"/>
     <col min="11" max="11" width="4.375" style="3" customWidth="1"/>
-    <col min="12" max="219" width="9" style="3"/>
-    <col min="220" max="220" width="5.5" style="3" customWidth="1"/>
-    <col min="221" max="221" width="22.125" style="3" customWidth="1"/>
-    <col min="222" max="222" width="14.75" style="3" customWidth="1"/>
-    <col min="223" max="223" width="37.75" style="3" customWidth="1"/>
-    <col min="224" max="224" width="10.375" style="3" customWidth="1"/>
-    <col min="225" max="225" width="7.125" style="3" customWidth="1"/>
-    <col min="226" max="226" width="5.5" style="3" customWidth="1"/>
-    <col min="227" max="227" width="7.625" style="3" customWidth="1"/>
-    <col min="228" max="228" width="14.5" style="3" customWidth="1"/>
-    <col min="229" max="229" width="28.125" style="3" customWidth="1"/>
-    <col min="230" max="230" width="9" style="3" customWidth="1"/>
-    <col min="231" max="231" width="13.875" style="3" customWidth="1"/>
-    <col min="232" max="475" width="9" style="3"/>
-    <col min="476" max="476" width="5.5" style="3" customWidth="1"/>
-    <col min="477" max="477" width="22.125" style="3" customWidth="1"/>
-    <col min="478" max="478" width="14.75" style="3" customWidth="1"/>
-    <col min="479" max="479" width="37.75" style="3" customWidth="1"/>
-    <col min="480" max="480" width="10.375" style="3" customWidth="1"/>
-    <col min="481" max="481" width="7.125" style="3" customWidth="1"/>
-    <col min="482" max="482" width="5.5" style="3" customWidth="1"/>
-    <col min="483" max="483" width="7.625" style="3" customWidth="1"/>
-    <col min="484" max="484" width="14.5" style="3" customWidth="1"/>
-    <col min="485" max="485" width="28.125" style="3" customWidth="1"/>
-    <col min="486" max="486" width="9" style="3" customWidth="1"/>
-    <col min="487" max="487" width="13.875" style="3" customWidth="1"/>
-    <col min="488" max="731" width="9" style="3"/>
-    <col min="732" max="732" width="5.5" style="3" customWidth="1"/>
-    <col min="733" max="733" width="22.125" style="3" customWidth="1"/>
-    <col min="734" max="734" width="14.75" style="3" customWidth="1"/>
-    <col min="735" max="735" width="37.75" style="3" customWidth="1"/>
-    <col min="736" max="736" width="10.375" style="3" customWidth="1"/>
-    <col min="737" max="737" width="7.125" style="3" customWidth="1"/>
-    <col min="738" max="738" width="5.5" style="3" customWidth="1"/>
-    <col min="739" max="739" width="7.625" style="3" customWidth="1"/>
-    <col min="740" max="740" width="14.5" style="3" customWidth="1"/>
-    <col min="741" max="741" width="28.125" style="3" customWidth="1"/>
-    <col min="742" max="742" width="9" style="3" customWidth="1"/>
-    <col min="743" max="743" width="13.875" style="3" customWidth="1"/>
-    <col min="744" max="987" width="9" style="3"/>
-    <col min="988" max="988" width="5.5" style="3" customWidth="1"/>
-    <col min="989" max="989" width="22.125" style="3" customWidth="1"/>
-    <col min="990" max="990" width="14.75" style="3" customWidth="1"/>
-    <col min="991" max="991" width="37.75" style="3" customWidth="1"/>
-    <col min="992" max="992" width="10.375" style="3" customWidth="1"/>
-    <col min="993" max="993" width="7.125" style="3" customWidth="1"/>
-    <col min="994" max="994" width="5.5" style="3" customWidth="1"/>
-    <col min="995" max="995" width="7.625" style="3" customWidth="1"/>
-    <col min="996" max="996" width="14.5" style="3" customWidth="1"/>
-    <col min="997" max="997" width="28.125" style="3" customWidth="1"/>
-    <col min="998" max="998" width="9" style="3" customWidth="1"/>
-    <col min="999" max="999" width="13.875" style="3" customWidth="1"/>
-    <col min="1000" max="1243" width="9" style="3"/>
-    <col min="1244" max="1244" width="5.5" style="3" customWidth="1"/>
-    <col min="1245" max="1245" width="22.125" style="3" customWidth="1"/>
-    <col min="1246" max="1246" width="14.75" style="3" customWidth="1"/>
-    <col min="1247" max="1247" width="37.75" style="3" customWidth="1"/>
-    <col min="1248" max="1248" width="10.375" style="3" customWidth="1"/>
-    <col min="1249" max="1249" width="7.125" style="3" customWidth="1"/>
-    <col min="1250" max="1250" width="5.5" style="3" customWidth="1"/>
-    <col min="1251" max="1251" width="7.625" style="3" customWidth="1"/>
-    <col min="1252" max="1252" width="14.5" style="3" customWidth="1"/>
-    <col min="1253" max="1253" width="28.125" style="3" customWidth="1"/>
-    <col min="1254" max="1254" width="9" style="3" customWidth="1"/>
-    <col min="1255" max="1255" width="13.875" style="3" customWidth="1"/>
-    <col min="1256" max="1499" width="9" style="3"/>
-    <col min="1500" max="1500" width="5.5" style="3" customWidth="1"/>
-    <col min="1501" max="1501" width="22.125" style="3" customWidth="1"/>
-    <col min="1502" max="1502" width="14.75" style="3" customWidth="1"/>
-    <col min="1503" max="1503" width="37.75" style="3" customWidth="1"/>
-    <col min="1504" max="1504" width="10.375" style="3" customWidth="1"/>
-    <col min="1505" max="1505" width="7.125" style="3" customWidth="1"/>
-    <col min="1506" max="1506" width="5.5" style="3" customWidth="1"/>
-    <col min="1507" max="1507" width="7.625" style="3" customWidth="1"/>
-    <col min="1508" max="1508" width="14.5" style="3" customWidth="1"/>
-    <col min="1509" max="1509" width="28.125" style="3" customWidth="1"/>
-    <col min="1510" max="1510" width="9" style="3" customWidth="1"/>
-    <col min="1511" max="1511" width="13.875" style="3" customWidth="1"/>
-    <col min="1512" max="1755" width="9" style="3"/>
-    <col min="1756" max="1756" width="5.5" style="3" customWidth="1"/>
-    <col min="1757" max="1757" width="22.125" style="3" customWidth="1"/>
-    <col min="1758" max="1758" width="14.75" style="3" customWidth="1"/>
-    <col min="1759" max="1759" width="37.75" style="3" customWidth="1"/>
-    <col min="1760" max="1760" width="10.375" style="3" customWidth="1"/>
-    <col min="1761" max="1761" width="7.125" style="3" customWidth="1"/>
-    <col min="1762" max="1762" width="5.5" style="3" customWidth="1"/>
-    <col min="1763" max="1763" width="7.625" style="3" customWidth="1"/>
-    <col min="1764" max="1764" width="14.5" style="3" customWidth="1"/>
-    <col min="1765" max="1765" width="28.125" style="3" customWidth="1"/>
-    <col min="1766" max="1766" width="9" style="3" customWidth="1"/>
-    <col min="1767" max="1767" width="13.875" style="3" customWidth="1"/>
-    <col min="1768" max="2011" width="9" style="3"/>
-    <col min="2012" max="2012" width="5.5" style="3" customWidth="1"/>
-    <col min="2013" max="2013" width="22.125" style="3" customWidth="1"/>
-    <col min="2014" max="2014" width="14.75" style="3" customWidth="1"/>
-    <col min="2015" max="2015" width="37.75" style="3" customWidth="1"/>
-    <col min="2016" max="2016" width="10.375" style="3" customWidth="1"/>
-    <col min="2017" max="2017" width="7.125" style="3" customWidth="1"/>
-    <col min="2018" max="2018" width="5.5" style="3" customWidth="1"/>
-    <col min="2019" max="2019" width="7.625" style="3" customWidth="1"/>
-    <col min="2020" max="2020" width="14.5" style="3" customWidth="1"/>
-    <col min="2021" max="2021" width="28.125" style="3" customWidth="1"/>
-    <col min="2022" max="2022" width="9" style="3" customWidth="1"/>
-    <col min="2023" max="2023" width="13.875" style="3" customWidth="1"/>
-    <col min="2024" max="2267" width="9" style="3"/>
-    <col min="2268" max="2268" width="5.5" style="3" customWidth="1"/>
-    <col min="2269" max="2269" width="22.125" style="3" customWidth="1"/>
-    <col min="2270" max="2270" width="14.75" style="3" customWidth="1"/>
-    <col min="2271" max="2271" width="37.75" style="3" customWidth="1"/>
-    <col min="2272" max="2272" width="10.375" style="3" customWidth="1"/>
-    <col min="2273" max="2273" width="7.125" style="3" customWidth="1"/>
-    <col min="2274" max="2274" width="5.5" style="3" customWidth="1"/>
-    <col min="2275" max="2275" width="7.625" style="3" customWidth="1"/>
-    <col min="2276" max="2276" width="14.5" style="3" customWidth="1"/>
-    <col min="2277" max="2277" width="28.125" style="3" customWidth="1"/>
-    <col min="2278" max="2278" width="9" style="3" customWidth="1"/>
-    <col min="2279" max="2279" width="13.875" style="3" customWidth="1"/>
-    <col min="2280" max="2523" width="9" style="3"/>
-    <col min="2524" max="2524" width="5.5" style="3" customWidth="1"/>
-    <col min="2525" max="2525" width="22.125" style="3" customWidth="1"/>
-    <col min="2526" max="2526" width="14.75" style="3" customWidth="1"/>
-    <col min="2527" max="2527" width="37.75" style="3" customWidth="1"/>
-    <col min="2528" max="2528" width="10.375" style="3" customWidth="1"/>
-    <col min="2529" max="2529" width="7.125" style="3" customWidth="1"/>
-    <col min="2530" max="2530" width="5.5" style="3" customWidth="1"/>
-    <col min="2531" max="2531" width="7.625" style="3" customWidth="1"/>
-    <col min="2532" max="2532" width="14.5" style="3" customWidth="1"/>
-    <col min="2533" max="2533" width="28.125" style="3" customWidth="1"/>
-    <col min="2534" max="2534" width="9" style="3" customWidth="1"/>
-    <col min="2535" max="2535" width="13.875" style="3" customWidth="1"/>
-    <col min="2536" max="2779" width="9" style="3"/>
-    <col min="2780" max="2780" width="5.5" style="3" customWidth="1"/>
-    <col min="2781" max="2781" width="22.125" style="3" customWidth="1"/>
-    <col min="2782" max="2782" width="14.75" style="3" customWidth="1"/>
-    <col min="2783" max="2783" width="37.75" style="3" customWidth="1"/>
-    <col min="2784" max="2784" width="10.375" style="3" customWidth="1"/>
-    <col min="2785" max="2785" width="7.125" style="3" customWidth="1"/>
-    <col min="2786" max="2786" width="5.5" style="3" customWidth="1"/>
-    <col min="2787" max="2787" width="7.625" style="3" customWidth="1"/>
-    <col min="2788" max="2788" width="14.5" style="3" customWidth="1"/>
-    <col min="2789" max="2789" width="28.125" style="3" customWidth="1"/>
-    <col min="2790" max="2790" width="9" style="3" customWidth="1"/>
-    <col min="2791" max="2791" width="13.875" style="3" customWidth="1"/>
-    <col min="2792" max="3035" width="9" style="3"/>
-    <col min="3036" max="3036" width="5.5" style="3" customWidth="1"/>
-    <col min="3037" max="3037" width="22.125" style="3" customWidth="1"/>
-    <col min="3038" max="3038" width="14.75" style="3" customWidth="1"/>
-    <col min="3039" max="3039" width="37.75" style="3" customWidth="1"/>
-    <col min="3040" max="3040" width="10.375" style="3" customWidth="1"/>
-    <col min="3041" max="3041" width="7.125" style="3" customWidth="1"/>
-    <col min="3042" max="3042" width="5.5" style="3" customWidth="1"/>
-    <col min="3043" max="3043" width="7.625" style="3" customWidth="1"/>
-    <col min="3044" max="3044" width="14.5" style="3" customWidth="1"/>
-    <col min="3045" max="3045" width="28.125" style="3" customWidth="1"/>
-    <col min="3046" max="3046" width="9" style="3" customWidth="1"/>
-    <col min="3047" max="3047" width="13.875" style="3" customWidth="1"/>
-    <col min="3048" max="3291" width="9" style="3"/>
-    <col min="3292" max="3292" width="5.5" style="3" customWidth="1"/>
-    <col min="3293" max="3293" width="22.125" style="3" customWidth="1"/>
-    <col min="3294" max="3294" width="14.75" style="3" customWidth="1"/>
-    <col min="3295" max="3295" width="37.75" style="3" customWidth="1"/>
-    <col min="3296" max="3296" width="10.375" style="3" customWidth="1"/>
-    <col min="3297" max="3297" width="7.125" style="3" customWidth="1"/>
-    <col min="3298" max="3298" width="5.5" style="3" customWidth="1"/>
-    <col min="3299" max="3299" width="7.625" style="3" customWidth="1"/>
-    <col min="3300" max="3300" width="14.5" style="3" customWidth="1"/>
-    <col min="3301" max="3301" width="28.125" style="3" customWidth="1"/>
-    <col min="3302" max="3302" width="9" style="3" customWidth="1"/>
-    <col min="3303" max="3303" width="13.875" style="3" customWidth="1"/>
-    <col min="3304" max="3547" width="9" style="3"/>
-    <col min="3548" max="3548" width="5.5" style="3" customWidth="1"/>
-    <col min="3549" max="3549" width="22.125" style="3" customWidth="1"/>
-    <col min="3550" max="3550" width="14.75" style="3" customWidth="1"/>
-    <col min="3551" max="3551" width="37.75" style="3" customWidth="1"/>
-    <col min="3552" max="3552" width="10.375" style="3" customWidth="1"/>
-    <col min="3553" max="3553" width="7.125" style="3" customWidth="1"/>
-    <col min="3554" max="3554" width="5.5" style="3" customWidth="1"/>
-    <col min="3555" max="3555" width="7.625" style="3" customWidth="1"/>
-    <col min="3556" max="3556" width="14.5" style="3" customWidth="1"/>
-    <col min="3557" max="3557" width="28.125" style="3" customWidth="1"/>
-    <col min="3558" max="3558" width="9" style="3" customWidth="1"/>
-    <col min="3559" max="3559" width="13.875" style="3" customWidth="1"/>
-    <col min="3560" max="3803" width="9" style="3"/>
-    <col min="3804" max="3804" width="5.5" style="3" customWidth="1"/>
-    <col min="3805" max="3805" width="22.125" style="3" customWidth="1"/>
-    <col min="3806" max="3806" width="14.75" style="3" customWidth="1"/>
-    <col min="3807" max="3807" width="37.75" style="3" customWidth="1"/>
-    <col min="3808" max="3808" width="10.375" style="3" customWidth="1"/>
-    <col min="3809" max="3809" width="7.125" style="3" customWidth="1"/>
-    <col min="3810" max="3810" width="5.5" style="3" customWidth="1"/>
-    <col min="3811" max="3811" width="7.625" style="3" customWidth="1"/>
-    <col min="3812" max="3812" width="14.5" style="3" customWidth="1"/>
-    <col min="3813" max="3813" width="28.125" style="3" customWidth="1"/>
-    <col min="3814" max="3814" width="9" style="3" customWidth="1"/>
-    <col min="3815" max="3815" width="13.875" style="3" customWidth="1"/>
-    <col min="3816" max="4059" width="9" style="3"/>
-    <col min="4060" max="4060" width="5.5" style="3" customWidth="1"/>
-    <col min="4061" max="4061" width="22.125" style="3" customWidth="1"/>
-    <col min="4062" max="4062" width="14.75" style="3" customWidth="1"/>
-    <col min="4063" max="4063" width="37.75" style="3" customWidth="1"/>
-    <col min="4064" max="4064" width="10.375" style="3" customWidth="1"/>
-    <col min="4065" max="4065" width="7.125" style="3" customWidth="1"/>
-    <col min="4066" max="4066" width="5.5" style="3" customWidth="1"/>
-    <col min="4067" max="4067" width="7.625" style="3" customWidth="1"/>
-    <col min="4068" max="4068" width="14.5" style="3" customWidth="1"/>
-    <col min="4069" max="4069" width="28.125" style="3" customWidth="1"/>
-    <col min="4070" max="4070" width="9" style="3" customWidth="1"/>
-    <col min="4071" max="4071" width="13.875" style="3" customWidth="1"/>
-    <col min="4072" max="4315" width="9" style="3"/>
-    <col min="4316" max="4316" width="5.5" style="3" customWidth="1"/>
-    <col min="4317" max="4317" width="22.125" style="3" customWidth="1"/>
-    <col min="4318" max="4318" width="14.75" style="3" customWidth="1"/>
-    <col min="4319" max="4319" width="37.75" style="3" customWidth="1"/>
-    <col min="4320" max="4320" width="10.375" style="3" customWidth="1"/>
-    <col min="4321" max="4321" width="7.125" style="3" customWidth="1"/>
-    <col min="4322" max="4322" width="5.5" style="3" customWidth="1"/>
-    <col min="4323" max="4323" width="7.625" style="3" customWidth="1"/>
-    <col min="4324" max="4324" width="14.5" style="3" customWidth="1"/>
-    <col min="4325" max="4325" width="28.125" style="3" customWidth="1"/>
-    <col min="4326" max="4326" width="9" style="3" customWidth="1"/>
-    <col min="4327" max="4327" width="13.875" style="3" customWidth="1"/>
-    <col min="4328" max="4571" width="9" style="3"/>
-    <col min="4572" max="4572" width="5.5" style="3" customWidth="1"/>
-    <col min="4573" max="4573" width="22.125" style="3" customWidth="1"/>
-    <col min="4574" max="4574" width="14.75" style="3" customWidth="1"/>
-    <col min="4575" max="4575" width="37.75" style="3" customWidth="1"/>
-    <col min="4576" max="4576" width="10.375" style="3" customWidth="1"/>
-    <col min="4577" max="4577" width="7.125" style="3" customWidth="1"/>
-    <col min="4578" max="4578" width="5.5" style="3" customWidth="1"/>
-    <col min="4579" max="4579" width="7.625" style="3" customWidth="1"/>
-    <col min="4580" max="4580" width="14.5" style="3" customWidth="1"/>
-    <col min="4581" max="4581" width="28.125" style="3" customWidth="1"/>
-    <col min="4582" max="4582" width="9" style="3" customWidth="1"/>
-    <col min="4583" max="4583" width="13.875" style="3" customWidth="1"/>
-    <col min="4584" max="4827" width="9" style="3"/>
-    <col min="4828" max="4828" width="5.5" style="3" customWidth="1"/>
-    <col min="4829" max="4829" width="22.125" style="3" customWidth="1"/>
-    <col min="4830" max="4830" width="14.75" style="3" customWidth="1"/>
-    <col min="4831" max="4831" width="37.75" style="3" customWidth="1"/>
-    <col min="4832" max="4832" width="10.375" style="3" customWidth="1"/>
-    <col min="4833" max="4833" width="7.125" style="3" customWidth="1"/>
-    <col min="4834" max="4834" width="5.5" style="3" customWidth="1"/>
-    <col min="4835" max="4835" width="7.625" style="3" customWidth="1"/>
-    <col min="4836" max="4836" width="14.5" style="3" customWidth="1"/>
-    <col min="4837" max="4837" width="28.125" style="3" customWidth="1"/>
-    <col min="4838" max="4838" width="9" style="3" customWidth="1"/>
-    <col min="4839" max="4839" width="13.875" style="3" customWidth="1"/>
-    <col min="4840" max="5083" width="9" style="3"/>
-    <col min="5084" max="5084" width="5.5" style="3" customWidth="1"/>
-    <col min="5085" max="5085" width="22.125" style="3" customWidth="1"/>
-    <col min="5086" max="5086" width="14.75" style="3" customWidth="1"/>
-    <col min="5087" max="5087" width="37.75" style="3" customWidth="1"/>
-    <col min="5088" max="5088" width="10.375" style="3" customWidth="1"/>
-    <col min="5089" max="5089" width="7.125" style="3" customWidth="1"/>
-    <col min="5090" max="5090" width="5.5" style="3" customWidth="1"/>
-    <col min="5091" max="5091" width="7.625" style="3" customWidth="1"/>
-    <col min="5092" max="5092" width="14.5" style="3" customWidth="1"/>
-    <col min="5093" max="5093" width="28.125" style="3" customWidth="1"/>
-    <col min="5094" max="5094" width="9" style="3" customWidth="1"/>
-    <col min="5095" max="5095" width="13.875" style="3" customWidth="1"/>
-    <col min="5096" max="5339" width="9" style="3"/>
-    <col min="5340" max="5340" width="5.5" style="3" customWidth="1"/>
-    <col min="5341" max="5341" width="22.125" style="3" customWidth="1"/>
-    <col min="5342" max="5342" width="14.75" style="3" customWidth="1"/>
-    <col min="5343" max="5343" width="37.75" style="3" customWidth="1"/>
-    <col min="5344" max="5344" width="10.375" style="3" customWidth="1"/>
-    <col min="5345" max="5345" width="7.125" style="3" customWidth="1"/>
-    <col min="5346" max="5346" width="5.5" style="3" customWidth="1"/>
-    <col min="5347" max="5347" width="7.625" style="3" customWidth="1"/>
-    <col min="5348" max="5348" width="14.5" style="3" customWidth="1"/>
-    <col min="5349" max="5349" width="28.125" style="3" customWidth="1"/>
-    <col min="5350" max="5350" width="9" style="3" customWidth="1"/>
-    <col min="5351" max="5351" width="13.875" style="3" customWidth="1"/>
-    <col min="5352" max="5595" width="9" style="3"/>
-    <col min="5596" max="5596" width="5.5" style="3" customWidth="1"/>
-    <col min="5597" max="5597" width="22.125" style="3" customWidth="1"/>
-    <col min="5598" max="5598" width="14.75" style="3" customWidth="1"/>
-    <col min="5599" max="5599" width="37.75" style="3" customWidth="1"/>
-    <col min="5600" max="5600" width="10.375" style="3" customWidth="1"/>
-    <col min="5601" max="5601" width="7.125" style="3" customWidth="1"/>
-    <col min="5602" max="5602" width="5.5" style="3" customWidth="1"/>
-    <col min="5603" max="5603" width="7.625" style="3" customWidth="1"/>
-    <col min="5604" max="5604" width="14.5" style="3" customWidth="1"/>
-    <col min="5605" max="5605" width="28.125" style="3" customWidth="1"/>
-    <col min="5606" max="5606" width="9" style="3" customWidth="1"/>
-    <col min="5607" max="5607" width="13.875" style="3" customWidth="1"/>
-    <col min="5608" max="5851" width="9" style="3"/>
-    <col min="5852" max="5852" width="5.5" style="3" customWidth="1"/>
-    <col min="5853" max="5853" width="22.125" style="3" customWidth="1"/>
-    <col min="5854" max="5854" width="14.75" style="3" customWidth="1"/>
-    <col min="5855" max="5855" width="37.75" style="3" customWidth="1"/>
-    <col min="5856" max="5856" width="10.375" style="3" customWidth="1"/>
-    <col min="5857" max="5857" width="7.125" style="3" customWidth="1"/>
-    <col min="5858" max="5858" width="5.5" style="3" customWidth="1"/>
-    <col min="5859" max="5859" width="7.625" style="3" customWidth="1"/>
-    <col min="5860" max="5860" width="14.5" style="3" customWidth="1"/>
-    <col min="5861" max="5861" width="28.125" style="3" customWidth="1"/>
-    <col min="5862" max="5862" width="9" style="3" customWidth="1"/>
-    <col min="5863" max="5863" width="13.875" style="3" customWidth="1"/>
-    <col min="5864" max="6107" width="9" style="3"/>
-    <col min="6108" max="6108" width="5.5" style="3" customWidth="1"/>
-    <col min="6109" max="6109" width="22.125" style="3" customWidth="1"/>
-    <col min="6110" max="6110" width="14.75" style="3" customWidth="1"/>
-    <col min="6111" max="6111" width="37.75" style="3" customWidth="1"/>
-    <col min="6112" max="6112" width="10.375" style="3" customWidth="1"/>
-    <col min="6113" max="6113" width="7.125" style="3" customWidth="1"/>
-    <col min="6114" max="6114" width="5.5" style="3" customWidth="1"/>
-    <col min="6115" max="6115" width="7.625" style="3" customWidth="1"/>
-    <col min="6116" max="6116" width="14.5" style="3" customWidth="1"/>
-    <col min="6117" max="6117" width="28.125" style="3" customWidth="1"/>
-    <col min="6118" max="6118" width="9" style="3" customWidth="1"/>
-    <col min="6119" max="6119" width="13.875" style="3" customWidth="1"/>
-    <col min="6120" max="6363" width="9" style="3"/>
-    <col min="6364" max="6364" width="5.5" style="3" customWidth="1"/>
-    <col min="6365" max="6365" width="22.125" style="3" customWidth="1"/>
-    <col min="6366" max="6366" width="14.75" style="3" customWidth="1"/>
-    <col min="6367" max="6367" width="37.75" style="3" customWidth="1"/>
-    <col min="6368" max="6368" width="10.375" style="3" customWidth="1"/>
-    <col min="6369" max="6369" width="7.125" style="3" customWidth="1"/>
-    <col min="6370" max="6370" width="5.5" style="3" customWidth="1"/>
-    <col min="6371" max="6371" width="7.625" style="3" customWidth="1"/>
-    <col min="6372" max="6372" width="14.5" style="3" customWidth="1"/>
-    <col min="6373" max="6373" width="28.125" style="3" customWidth="1"/>
-    <col min="6374" max="6374" width="9" style="3" customWidth="1"/>
-    <col min="6375" max="6375" width="13.875" style="3" customWidth="1"/>
-    <col min="6376" max="6619" width="9" style="3"/>
-    <col min="6620" max="6620" width="5.5" style="3" customWidth="1"/>
-    <col min="6621" max="6621" width="22.125" style="3" customWidth="1"/>
-    <col min="6622" max="6622" width="14.75" style="3" customWidth="1"/>
-    <col min="6623" max="6623" width="37.75" style="3" customWidth="1"/>
-    <col min="6624" max="6624" width="10.375" style="3" customWidth="1"/>
-    <col min="6625" max="6625" width="7.125" style="3" customWidth="1"/>
-    <col min="6626" max="6626" width="5.5" style="3" customWidth="1"/>
-    <col min="6627" max="6627" width="7.625" style="3" customWidth="1"/>
-    <col min="6628" max="6628" width="14.5" style="3" customWidth="1"/>
-    <col min="6629" max="6629" width="28.125" style="3" customWidth="1"/>
-    <col min="6630" max="6630" width="9" style="3" customWidth="1"/>
-    <col min="6631" max="6631" width="13.875" style="3" customWidth="1"/>
-    <col min="6632" max="6875" width="9" style="3"/>
-    <col min="6876" max="6876" width="5.5" style="3" customWidth="1"/>
-    <col min="6877" max="6877" width="22.125" style="3" customWidth="1"/>
-    <col min="6878" max="6878" width="14.75" style="3" customWidth="1"/>
-    <col min="6879" max="6879" width="37.75" style="3" customWidth="1"/>
-    <col min="6880" max="6880" width="10.375" style="3" customWidth="1"/>
-    <col min="6881" max="6881" width="7.125" style="3" customWidth="1"/>
-    <col min="6882" max="6882" width="5.5" style="3" customWidth="1"/>
-    <col min="6883" max="6883" width="7.625" style="3" customWidth="1"/>
-    <col min="6884" max="6884" width="14.5" style="3" customWidth="1"/>
-    <col min="6885" max="6885" width="28.125" style="3" customWidth="1"/>
-    <col min="6886" max="6886" width="9" style="3" customWidth="1"/>
-    <col min="6887" max="6887" width="13.875" style="3" customWidth="1"/>
-    <col min="6888" max="7131" width="9" style="3"/>
-    <col min="7132" max="7132" width="5.5" style="3" customWidth="1"/>
-    <col min="7133" max="7133" width="22.125" style="3" customWidth="1"/>
-    <col min="7134" max="7134" width="14.75" style="3" customWidth="1"/>
-    <col min="7135" max="7135" width="37.75" style="3" customWidth="1"/>
-    <col min="7136" max="7136" width="10.375" style="3" customWidth="1"/>
-    <col min="7137" max="7137" width="7.125" style="3" customWidth="1"/>
-    <col min="7138" max="7138" width="5.5" style="3" customWidth="1"/>
-    <col min="7139" max="7139" width="7.625" style="3" customWidth="1"/>
-    <col min="7140" max="7140" width="14.5" style="3" customWidth="1"/>
-    <col min="7141" max="7141" width="28.125" style="3" customWidth="1"/>
-    <col min="7142" max="7142" width="9" style="3" customWidth="1"/>
-    <col min="7143" max="7143" width="13.875" style="3" customWidth="1"/>
-    <col min="7144" max="7387" width="9" style="3"/>
-    <col min="7388" max="7388" width="5.5" style="3" customWidth="1"/>
-    <col min="7389" max="7389" width="22.125" style="3" customWidth="1"/>
-    <col min="7390" max="7390" width="14.75" style="3" customWidth="1"/>
-    <col min="7391" max="7391" width="37.75" style="3" customWidth="1"/>
-    <col min="7392" max="7392" width="10.375" style="3" customWidth="1"/>
-    <col min="7393" max="7393" width="7.125" style="3" customWidth="1"/>
-    <col min="7394" max="7394" width="5.5" style="3" customWidth="1"/>
-    <col min="7395" max="7395" width="7.625" style="3" customWidth="1"/>
-    <col min="7396" max="7396" width="14.5" style="3" customWidth="1"/>
-    <col min="7397" max="7397" width="28.125" style="3" customWidth="1"/>
-    <col min="7398" max="7398" width="9" style="3" customWidth="1"/>
-    <col min="7399" max="7399" width="13.875" style="3" customWidth="1"/>
-    <col min="7400" max="7643" width="9" style="3"/>
-    <col min="7644" max="7644" width="5.5" style="3" customWidth="1"/>
-    <col min="7645" max="7645" width="22.125" style="3" customWidth="1"/>
-    <col min="7646" max="7646" width="14.75" style="3" customWidth="1"/>
-    <col min="7647" max="7647" width="37.75" style="3" customWidth="1"/>
-    <col min="7648" max="7648" width="10.375" style="3" customWidth="1"/>
-    <col min="7649" max="7649" width="7.125" style="3" customWidth="1"/>
-    <col min="7650" max="7650" width="5.5" style="3" customWidth="1"/>
-    <col min="7651" max="7651" width="7.625" style="3" customWidth="1"/>
-    <col min="7652" max="7652" width="14.5" style="3" customWidth="1"/>
-    <col min="7653" max="7653" width="28.125" style="3" customWidth="1"/>
-    <col min="7654" max="7654" width="9" style="3" customWidth="1"/>
-    <col min="7655" max="7655" width="13.875" style="3" customWidth="1"/>
-    <col min="7656" max="7899" width="9" style="3"/>
-    <col min="7900" max="7900" width="5.5" style="3" customWidth="1"/>
-    <col min="7901" max="7901" width="22.125" style="3" customWidth="1"/>
-    <col min="7902" max="7902" width="14.75" style="3" customWidth="1"/>
-    <col min="7903" max="7903" width="37.75" style="3" customWidth="1"/>
-    <col min="7904" max="7904" width="10.375" style="3" customWidth="1"/>
-    <col min="7905" max="7905" width="7.125" style="3" customWidth="1"/>
-    <col min="7906" max="7906" width="5.5" style="3" customWidth="1"/>
-    <col min="7907" max="7907" width="7.625" style="3" customWidth="1"/>
-    <col min="7908" max="7908" width="14.5" style="3" customWidth="1"/>
-    <col min="7909" max="7909" width="28.125" style="3" customWidth="1"/>
-    <col min="7910" max="7910" width="9" style="3" customWidth="1"/>
-    <col min="7911" max="7911" width="13.875" style="3" customWidth="1"/>
-    <col min="7912" max="8155" width="9" style="3"/>
-    <col min="8156" max="8156" width="5.5" style="3" customWidth="1"/>
-    <col min="8157" max="8157" width="22.125" style="3" customWidth="1"/>
-    <col min="8158" max="8158" width="14.75" style="3" customWidth="1"/>
-    <col min="8159" max="8159" width="37.75" style="3" customWidth="1"/>
-    <col min="8160" max="8160" width="10.375" style="3" customWidth="1"/>
-    <col min="8161" max="8161" width="7.125" style="3" customWidth="1"/>
-    <col min="8162" max="8162" width="5.5" style="3" customWidth="1"/>
-    <col min="8163" max="8163" width="7.625" style="3" customWidth="1"/>
-    <col min="8164" max="8164" width="14.5" style="3" customWidth="1"/>
-    <col min="8165" max="8165" width="28.125" style="3" customWidth="1"/>
-    <col min="8166" max="8166" width="9" style="3" customWidth="1"/>
-    <col min="8167" max="8167" width="13.875" style="3" customWidth="1"/>
-    <col min="8168" max="8411" width="9" style="3"/>
-    <col min="8412" max="8412" width="5.5" style="3" customWidth="1"/>
-    <col min="8413" max="8413" width="22.125" style="3" customWidth="1"/>
-    <col min="8414" max="8414" width="14.75" style="3" customWidth="1"/>
-    <col min="8415" max="8415" width="37.75" style="3" customWidth="1"/>
-    <col min="8416" max="8416" width="10.375" style="3" customWidth="1"/>
-    <col min="8417" max="8417" width="7.125" style="3" customWidth="1"/>
-    <col min="8418" max="8418" width="5.5" style="3" customWidth="1"/>
-    <col min="8419" max="8419" width="7.625" style="3" customWidth="1"/>
-    <col min="8420" max="8420" width="14.5" style="3" customWidth="1"/>
-    <col min="8421" max="8421" width="28.125" style="3" customWidth="1"/>
-    <col min="8422" max="8422" width="9" style="3" customWidth="1"/>
-    <col min="8423" max="8423" width="13.875" style="3" customWidth="1"/>
-    <col min="8424" max="8667" width="9" style="3"/>
-    <col min="8668" max="8668" width="5.5" style="3" customWidth="1"/>
-    <col min="8669" max="8669" width="22.125" style="3" customWidth="1"/>
-    <col min="8670" max="8670" width="14.75" style="3" customWidth="1"/>
-    <col min="8671" max="8671" width="37.75" style="3" customWidth="1"/>
-    <col min="8672" max="8672" width="10.375" style="3" customWidth="1"/>
-    <col min="8673" max="8673" width="7.125" style="3" customWidth="1"/>
-    <col min="8674" max="8674" width="5.5" style="3" customWidth="1"/>
-    <col min="8675" max="8675" width="7.625" style="3" customWidth="1"/>
-    <col min="8676" max="8676" width="14.5" style="3" customWidth="1"/>
-    <col min="8677" max="8677" width="28.125" style="3" customWidth="1"/>
-    <col min="8678" max="8678" width="9" style="3" customWidth="1"/>
-    <col min="8679" max="8679" width="13.875" style="3" customWidth="1"/>
-    <col min="8680" max="8923" width="9" style="3"/>
-    <col min="8924" max="8924" width="5.5" style="3" customWidth="1"/>
-    <col min="8925" max="8925" width="22.125" style="3" customWidth="1"/>
-    <col min="8926" max="8926" width="14.75" style="3" customWidth="1"/>
-    <col min="8927" max="8927" width="37.75" style="3" customWidth="1"/>
-    <col min="8928" max="8928" width="10.375" style="3" customWidth="1"/>
-    <col min="8929" max="8929" width="7.125" style="3" customWidth="1"/>
-    <col min="8930" max="8930" width="5.5" style="3" customWidth="1"/>
-    <col min="8931" max="8931" width="7.625" style="3" customWidth="1"/>
-    <col min="8932" max="8932" width="14.5" style="3" customWidth="1"/>
-    <col min="8933" max="8933" width="28.125" style="3" customWidth="1"/>
-    <col min="8934" max="8934" width="9" style="3" customWidth="1"/>
-    <col min="8935" max="8935" width="13.875" style="3" customWidth="1"/>
-    <col min="8936" max="9179" width="9" style="3"/>
-    <col min="9180" max="9180" width="5.5" style="3" customWidth="1"/>
-    <col min="9181" max="9181" width="22.125" style="3" customWidth="1"/>
-    <col min="9182" max="9182" width="14.75" style="3" customWidth="1"/>
-    <col min="9183" max="9183" width="37.75" style="3" customWidth="1"/>
-    <col min="9184" max="9184" width="10.375" style="3" customWidth="1"/>
-    <col min="9185" max="9185" width="7.125" style="3" customWidth="1"/>
-    <col min="9186" max="9186" width="5.5" style="3" customWidth="1"/>
-    <col min="9187" max="9187" width="7.625" style="3" customWidth="1"/>
-    <col min="9188" max="9188" width="14.5" style="3" customWidth="1"/>
-    <col min="9189" max="9189" width="28.125" style="3" customWidth="1"/>
-    <col min="9190" max="9190" width="9" style="3" customWidth="1"/>
-    <col min="9191" max="9191" width="13.875" style="3" customWidth="1"/>
-    <col min="9192" max="9435" width="9" style="3"/>
-    <col min="9436" max="9436" width="5.5" style="3" customWidth="1"/>
-    <col min="9437" max="9437" width="22.125" style="3" customWidth="1"/>
-    <col min="9438" max="9438" width="14.75" style="3" customWidth="1"/>
-    <col min="9439" max="9439" width="37.75" style="3" customWidth="1"/>
-    <col min="9440" max="9440" width="10.375" style="3" customWidth="1"/>
-    <col min="9441" max="9441" width="7.125" style="3" customWidth="1"/>
-    <col min="9442" max="9442" width="5.5" style="3" customWidth="1"/>
-    <col min="9443" max="9443" width="7.625" style="3" customWidth="1"/>
-    <col min="9444" max="9444" width="14.5" style="3" customWidth="1"/>
-    <col min="9445" max="9445" width="28.125" style="3" customWidth="1"/>
-    <col min="9446" max="9446" width="9" style="3" customWidth="1"/>
-    <col min="9447" max="9447" width="13.875" style="3" customWidth="1"/>
-    <col min="9448" max="9691" width="9" style="3"/>
-    <col min="9692" max="9692" width="5.5" style="3" customWidth="1"/>
-    <col min="9693" max="9693" width="22.125" style="3" customWidth="1"/>
-    <col min="9694" max="9694" width="14.75" style="3" customWidth="1"/>
-    <col min="9695" max="9695" width="37.75" style="3" customWidth="1"/>
-    <col min="9696" max="9696" width="10.375" style="3" customWidth="1"/>
-    <col min="9697" max="9697" width="7.125" style="3" customWidth="1"/>
-    <col min="9698" max="9698" width="5.5" style="3" customWidth="1"/>
-    <col min="9699" max="9699" width="7.625" style="3" customWidth="1"/>
-    <col min="9700" max="9700" width="14.5" style="3" customWidth="1"/>
-    <col min="9701" max="9701" width="28.125" style="3" customWidth="1"/>
-    <col min="9702" max="9702" width="9" style="3" customWidth="1"/>
-    <col min="9703" max="9703" width="13.875" style="3" customWidth="1"/>
-    <col min="9704" max="9947" width="9" style="3"/>
-    <col min="9948" max="9948" width="5.5" style="3" customWidth="1"/>
-    <col min="9949" max="9949" width="22.125" style="3" customWidth="1"/>
-    <col min="9950" max="9950" width="14.75" style="3" customWidth="1"/>
-    <col min="9951" max="9951" width="37.75" style="3" customWidth="1"/>
-    <col min="9952" max="9952" width="10.375" style="3" customWidth="1"/>
-    <col min="9953" max="9953" width="7.125" style="3" customWidth="1"/>
-    <col min="9954" max="9954" width="5.5" style="3" customWidth="1"/>
-    <col min="9955" max="9955" width="7.625" style="3" customWidth="1"/>
-    <col min="9956" max="9956" width="14.5" style="3" customWidth="1"/>
-    <col min="9957" max="9957" width="28.125" style="3" customWidth="1"/>
-    <col min="9958" max="9958" width="9" style="3" customWidth="1"/>
-    <col min="9959" max="9959" width="13.875" style="3" customWidth="1"/>
-    <col min="9960" max="10203" width="9" style="3"/>
-    <col min="10204" max="10204" width="5.5" style="3" customWidth="1"/>
-    <col min="10205" max="10205" width="22.125" style="3" customWidth="1"/>
-    <col min="10206" max="10206" width="14.75" style="3" customWidth="1"/>
-    <col min="10207" max="10207" width="37.75" style="3" customWidth="1"/>
-    <col min="10208" max="10208" width="10.375" style="3" customWidth="1"/>
-    <col min="10209" max="10209" width="7.125" style="3" customWidth="1"/>
-    <col min="10210" max="10210" width="5.5" style="3" customWidth="1"/>
-    <col min="10211" max="10211" width="7.625" style="3" customWidth="1"/>
-    <col min="10212" max="10212" width="14.5" style="3" customWidth="1"/>
-    <col min="10213" max="10213" width="28.125" style="3" customWidth="1"/>
-    <col min="10214" max="10214" width="9" style="3" customWidth="1"/>
-    <col min="10215" max="10215" width="13.875" style="3" customWidth="1"/>
-    <col min="10216" max="10459" width="9" style="3"/>
-    <col min="10460" max="10460" width="5.5" style="3" customWidth="1"/>
-    <col min="10461" max="10461" width="22.125" style="3" customWidth="1"/>
-    <col min="10462" max="10462" width="14.75" style="3" customWidth="1"/>
-    <col min="10463" max="10463" width="37.75" style="3" customWidth="1"/>
-    <col min="10464" max="10464" width="10.375" style="3" customWidth="1"/>
-    <col min="10465" max="10465" width="7.125" style="3" customWidth="1"/>
-    <col min="10466" max="10466" width="5.5" style="3" customWidth="1"/>
-    <col min="10467" max="10467" width="7.625" style="3" customWidth="1"/>
-    <col min="10468" max="10468" width="14.5" style="3" customWidth="1"/>
-    <col min="10469" max="10469" width="28.125" style="3" customWidth="1"/>
-    <col min="10470" max="10470" width="9" style="3" customWidth="1"/>
-    <col min="10471" max="10471" width="13.875" style="3" customWidth="1"/>
-    <col min="10472" max="10715" width="9" style="3"/>
-    <col min="10716" max="10716" width="5.5" style="3" customWidth="1"/>
-    <col min="10717" max="10717" width="22.125" style="3" customWidth="1"/>
-    <col min="10718" max="10718" width="14.75" style="3" customWidth="1"/>
-    <col min="10719" max="10719" width="37.75" style="3" customWidth="1"/>
-    <col min="10720" max="10720" width="10.375" style="3" customWidth="1"/>
-    <col min="10721" max="10721" width="7.125" style="3" customWidth="1"/>
-    <col min="10722" max="10722" width="5.5" style="3" customWidth="1"/>
-    <col min="10723" max="10723" width="7.625" style="3" customWidth="1"/>
-    <col min="10724" max="10724" width="14.5" style="3" customWidth="1"/>
-    <col min="10725" max="10725" width="28.125" style="3" customWidth="1"/>
-    <col min="10726" max="10726" width="9" style="3" customWidth="1"/>
-    <col min="10727" max="10727" width="13.875" style="3" customWidth="1"/>
-    <col min="10728" max="10971" width="9" style="3"/>
-    <col min="10972" max="10972" width="5.5" style="3" customWidth="1"/>
-    <col min="10973" max="10973" width="22.125" style="3" customWidth="1"/>
-    <col min="10974" max="10974" width="14.75" style="3" customWidth="1"/>
-    <col min="10975" max="10975" width="37.75" style="3" customWidth="1"/>
-    <col min="10976" max="10976" width="10.375" style="3" customWidth="1"/>
-    <col min="10977" max="10977" width="7.125" style="3" customWidth="1"/>
-    <col min="10978" max="10978" width="5.5" style="3" customWidth="1"/>
-    <col min="10979" max="10979" width="7.625" style="3" customWidth="1"/>
-    <col min="10980" max="10980" width="14.5" style="3" customWidth="1"/>
-    <col min="10981" max="10981" width="28.125" style="3" customWidth="1"/>
-    <col min="10982" max="10982" width="9" style="3" customWidth="1"/>
-    <col min="10983" max="10983" width="13.875" style="3" customWidth="1"/>
-    <col min="10984" max="11227" width="9" style="3"/>
-    <col min="11228" max="11228" width="5.5" style="3" customWidth="1"/>
-    <col min="11229" max="11229" width="22.125" style="3" customWidth="1"/>
-    <col min="11230" max="11230" width="14.75" style="3" customWidth="1"/>
-    <col min="11231" max="11231" width="37.75" style="3" customWidth="1"/>
-    <col min="11232" max="11232" width="10.375" style="3" customWidth="1"/>
-    <col min="11233" max="11233" width="7.125" style="3" customWidth="1"/>
-    <col min="11234" max="11234" width="5.5" style="3" customWidth="1"/>
-    <col min="11235" max="11235" width="7.625" style="3" customWidth="1"/>
-    <col min="11236" max="11236" width="14.5" style="3" customWidth="1"/>
-    <col min="11237" max="11237" width="28.125" style="3" customWidth="1"/>
-    <col min="11238" max="11238" width="9" style="3" customWidth="1"/>
-    <col min="11239" max="11239" width="13.875" style="3" customWidth="1"/>
-    <col min="11240" max="11483" width="9" style="3"/>
-    <col min="11484" max="11484" width="5.5" style="3" customWidth="1"/>
-    <col min="11485" max="11485" width="22.125" style="3" customWidth="1"/>
-    <col min="11486" max="11486" width="14.75" style="3" customWidth="1"/>
-    <col min="11487" max="11487" width="37.75" style="3" customWidth="1"/>
-    <col min="11488" max="11488" width="10.375" style="3" customWidth="1"/>
-    <col min="11489" max="11489" width="7.125" style="3" customWidth="1"/>
-    <col min="11490" max="11490" width="5.5" style="3" customWidth="1"/>
-    <col min="11491" max="11491" width="7.625" style="3" customWidth="1"/>
-    <col min="11492" max="11492" width="14.5" style="3" customWidth="1"/>
-    <col min="11493" max="11493" width="28.125" style="3" customWidth="1"/>
-    <col min="11494" max="11494" width="9" style="3" customWidth="1"/>
-    <col min="11495" max="11495" width="13.875" style="3" customWidth="1"/>
-    <col min="11496" max="11739" width="9" style="3"/>
-    <col min="11740" max="11740" width="5.5" style="3" customWidth="1"/>
-    <col min="11741" max="11741" width="22.125" style="3" customWidth="1"/>
-    <col min="11742" max="11742" width="14.75" style="3" customWidth="1"/>
-    <col min="11743" max="11743" width="37.75" style="3" customWidth="1"/>
-    <col min="11744" max="11744" width="10.375" style="3" customWidth="1"/>
-    <col min="11745" max="11745" width="7.125" style="3" customWidth="1"/>
-    <col min="11746" max="11746" width="5.5" style="3" customWidth="1"/>
-    <col min="11747" max="11747" width="7.625" style="3" customWidth="1"/>
-    <col min="11748" max="11748" width="14.5" style="3" customWidth="1"/>
-    <col min="11749" max="11749" width="28.125" style="3" customWidth="1"/>
-    <col min="11750" max="11750" width="9" style="3" customWidth="1"/>
-    <col min="11751" max="11751" width="13.875" style="3" customWidth="1"/>
-    <col min="11752" max="11995" width="9" style="3"/>
-    <col min="11996" max="11996" width="5.5" style="3" customWidth="1"/>
-    <col min="11997" max="11997" width="22.125" style="3" customWidth="1"/>
-    <col min="11998" max="11998" width="14.75" style="3" customWidth="1"/>
-    <col min="11999" max="11999" width="37.75" style="3" customWidth="1"/>
-    <col min="12000" max="12000" width="10.375" style="3" customWidth="1"/>
-    <col min="12001" max="12001" width="7.125" style="3" customWidth="1"/>
-    <col min="12002" max="12002" width="5.5" style="3" customWidth="1"/>
-    <col min="12003" max="12003" width="7.625" style="3" customWidth="1"/>
-    <col min="12004" max="12004" width="14.5" style="3" customWidth="1"/>
-    <col min="12005" max="12005" width="28.125" style="3" customWidth="1"/>
-    <col min="12006" max="12006" width="9" style="3" customWidth="1"/>
-    <col min="12007" max="12007" width="13.875" style="3" customWidth="1"/>
-    <col min="12008" max="12251" width="9" style="3"/>
-    <col min="12252" max="12252" width="5.5" style="3" customWidth="1"/>
-    <col min="12253" max="12253" width="22.125" style="3" customWidth="1"/>
-    <col min="12254" max="12254" width="14.75" style="3" customWidth="1"/>
-    <col min="12255" max="12255" width="37.75" style="3" customWidth="1"/>
-    <col min="12256" max="12256" width="10.375" style="3" customWidth="1"/>
-    <col min="12257" max="12257" width="7.125" style="3" customWidth="1"/>
-    <col min="12258" max="12258" width="5.5" style="3" customWidth="1"/>
-    <col min="12259" max="12259" width="7.625" style="3" customWidth="1"/>
-    <col min="12260" max="12260" width="14.5" style="3" customWidth="1"/>
-    <col min="12261" max="12261" width="28.125" style="3" customWidth="1"/>
-    <col min="12262" max="12262" width="9" style="3" customWidth="1"/>
-    <col min="12263" max="12263" width="13.875" style="3" customWidth="1"/>
-    <col min="12264" max="12507" width="9" style="3"/>
-    <col min="12508" max="12508" width="5.5" style="3" customWidth="1"/>
-    <col min="12509" max="12509" width="22.125" style="3" customWidth="1"/>
-    <col min="12510" max="12510" width="14.75" style="3" customWidth="1"/>
-    <col min="12511" max="12511" width="37.75" style="3" customWidth="1"/>
-    <col min="12512" max="12512" width="10.375" style="3" customWidth="1"/>
-    <col min="12513" max="12513" width="7.125" style="3" customWidth="1"/>
-    <col min="12514" max="12514" width="5.5" style="3" customWidth="1"/>
-    <col min="12515" max="12515" width="7.625" style="3" customWidth="1"/>
-    <col min="12516" max="12516" width="14.5" style="3" customWidth="1"/>
-    <col min="12517" max="12517" width="28.125" style="3" customWidth="1"/>
-    <col min="12518" max="12518" width="9" style="3" customWidth="1"/>
-    <col min="12519" max="12519" width="13.875" style="3" customWidth="1"/>
-    <col min="12520" max="12763" width="9" style="3"/>
-    <col min="12764" max="12764" width="5.5" style="3" customWidth="1"/>
-    <col min="12765" max="12765" width="22.125" style="3" customWidth="1"/>
-    <col min="12766" max="12766" width="14.75" style="3" customWidth="1"/>
-    <col min="12767" max="12767" width="37.75" style="3" customWidth="1"/>
-    <col min="12768" max="12768" width="10.375" style="3" customWidth="1"/>
-    <col min="12769" max="12769" width="7.125" style="3" customWidth="1"/>
-    <col min="12770" max="12770" width="5.5" style="3" customWidth="1"/>
-    <col min="12771" max="12771" width="7.625" style="3" customWidth="1"/>
-    <col min="12772" max="12772" width="14.5" style="3" customWidth="1"/>
-    <col min="12773" max="12773" width="28.125" style="3" customWidth="1"/>
-    <col min="12774" max="12774" width="9" style="3" customWidth="1"/>
-    <col min="12775" max="12775" width="13.875" style="3" customWidth="1"/>
-    <col min="12776" max="13019" width="9" style="3"/>
-    <col min="13020" max="13020" width="5.5" style="3" customWidth="1"/>
-    <col min="13021" max="13021" width="22.125" style="3" customWidth="1"/>
-    <col min="13022" max="13022" width="14.75" style="3" customWidth="1"/>
-    <col min="13023" max="13023" width="37.75" style="3" customWidth="1"/>
-    <col min="13024" max="13024" width="10.375" style="3" customWidth="1"/>
-    <col min="13025" max="13025" width="7.125" style="3" customWidth="1"/>
-    <col min="13026" max="13026" width="5.5" style="3" customWidth="1"/>
-    <col min="13027" max="13027" width="7.625" style="3" customWidth="1"/>
-    <col min="13028" max="13028" width="14.5" style="3" customWidth="1"/>
-    <col min="13029" max="13029" width="28.125" style="3" customWidth="1"/>
-    <col min="13030" max="13030" width="9" style="3" customWidth="1"/>
-    <col min="13031" max="13031" width="13.875" style="3" customWidth="1"/>
-    <col min="13032" max="13275" width="9" style="3"/>
-    <col min="13276" max="13276" width="5.5" style="3" customWidth="1"/>
-    <col min="13277" max="13277" width="22.125" style="3" customWidth="1"/>
-    <col min="13278" max="13278" width="14.75" style="3" customWidth="1"/>
-    <col min="13279" max="13279" width="37.75" style="3" customWidth="1"/>
-    <col min="13280" max="13280" width="10.375" style="3" customWidth="1"/>
-    <col min="13281" max="13281" width="7.125" style="3" customWidth="1"/>
-    <col min="13282" max="13282" width="5.5" style="3" customWidth="1"/>
-    <col min="13283" max="13283" width="7.625" style="3" customWidth="1"/>
-    <col min="13284" max="13284" width="14.5" style="3" customWidth="1"/>
-    <col min="13285" max="13285" width="28.125" style="3" customWidth="1"/>
-    <col min="13286" max="13286" width="9" style="3" customWidth="1"/>
-    <col min="13287" max="13287" width="13.875" style="3" customWidth="1"/>
-    <col min="13288" max="13531" width="9" style="3"/>
-    <col min="13532" max="13532" width="5.5" style="3" customWidth="1"/>
-    <col min="13533" max="13533" width="22.125" style="3" customWidth="1"/>
-    <col min="13534" max="13534" width="14.75" style="3" customWidth="1"/>
-    <col min="13535" max="13535" width="37.75" style="3" customWidth="1"/>
-    <col min="13536" max="13536" width="10.375" style="3" customWidth="1"/>
-    <col min="13537" max="13537" width="7.125" style="3" customWidth="1"/>
-    <col min="13538" max="13538" width="5.5" style="3" customWidth="1"/>
-    <col min="13539" max="13539" width="7.625" style="3" customWidth="1"/>
-    <col min="13540" max="13540" width="14.5" style="3" customWidth="1"/>
-    <col min="13541" max="13541" width="28.125" style="3" customWidth="1"/>
-    <col min="13542" max="13542" width="9" style="3" customWidth="1"/>
-    <col min="13543" max="13543" width="13.875" style="3" customWidth="1"/>
-    <col min="13544" max="13787" width="9" style="3"/>
-    <col min="13788" max="13788" width="5.5" style="3" customWidth="1"/>
-    <col min="13789" max="13789" width="22.125" style="3" customWidth="1"/>
-    <col min="13790" max="13790" width="14.75" style="3" customWidth="1"/>
-    <col min="13791" max="13791" width="37.75" style="3" customWidth="1"/>
-    <col min="13792" max="13792" width="10.375" style="3" customWidth="1"/>
-    <col min="13793" max="13793" width="7.125" style="3" customWidth="1"/>
-    <col min="13794" max="13794" width="5.5" style="3" customWidth="1"/>
-    <col min="13795" max="13795" width="7.625" style="3" customWidth="1"/>
-    <col min="13796" max="13796" width="14.5" style="3" customWidth="1"/>
-    <col min="13797" max="13797" width="28.125" style="3" customWidth="1"/>
-    <col min="13798" max="13798" width="9" style="3" customWidth="1"/>
-    <col min="13799" max="13799" width="13.875" style="3" customWidth="1"/>
-    <col min="13800" max="14043" width="9" style="3"/>
-    <col min="14044" max="14044" width="5.5" style="3" customWidth="1"/>
-    <col min="14045" max="14045" width="22.125" style="3" customWidth="1"/>
-    <col min="14046" max="14046" width="14.75" style="3" customWidth="1"/>
-    <col min="14047" max="14047" width="37.75" style="3" customWidth="1"/>
-    <col min="14048" max="14048" width="10.375" style="3" customWidth="1"/>
-    <col min="14049" max="14049" width="7.125" style="3" customWidth="1"/>
-    <col min="14050" max="14050" width="5.5" style="3" customWidth="1"/>
-    <col min="14051" max="14051" width="7.625" style="3" customWidth="1"/>
-    <col min="14052" max="14052" width="14.5" style="3" customWidth="1"/>
-    <col min="14053" max="14053" width="28.125" style="3" customWidth="1"/>
-    <col min="14054" max="14054" width="9" style="3" customWidth="1"/>
-    <col min="14055" max="14055" width="13.875" style="3" customWidth="1"/>
-    <col min="14056" max="14299" width="9" style="3"/>
-    <col min="14300" max="14300" width="5.5" style="3" customWidth="1"/>
-    <col min="14301" max="14301" width="22.125" style="3" customWidth="1"/>
-    <col min="14302" max="14302" width="14.75" style="3" customWidth="1"/>
-    <col min="14303" max="14303" width="37.75" style="3" customWidth="1"/>
-    <col min="14304" max="14304" width="10.375" style="3" customWidth="1"/>
-    <col min="14305" max="14305" width="7.125" style="3" customWidth="1"/>
-    <col min="14306" max="14306" width="5.5" style="3" customWidth="1"/>
-    <col min="14307" max="14307" width="7.625" style="3" customWidth="1"/>
-    <col min="14308" max="14308" width="14.5" style="3" customWidth="1"/>
-    <col min="14309" max="14309" width="28.125" style="3" customWidth="1"/>
-    <col min="14310" max="14310" width="9" style="3" customWidth="1"/>
-    <col min="14311" max="14311" width="13.875" style="3" customWidth="1"/>
-    <col min="14312" max="14555" width="9" style="3"/>
-    <col min="14556" max="14556" width="5.5" style="3" customWidth="1"/>
-    <col min="14557" max="14557" width="22.125" style="3" customWidth="1"/>
-    <col min="14558" max="14558" width="14.75" style="3" customWidth="1"/>
-    <col min="14559" max="14559" width="37.75" style="3" customWidth="1"/>
-    <col min="14560" max="14560" width="10.375" style="3" customWidth="1"/>
-    <col min="14561" max="14561" width="7.125" style="3" customWidth="1"/>
-    <col min="14562" max="14562" width="5.5" style="3" customWidth="1"/>
-    <col min="14563" max="14563" width="7.625" style="3" customWidth="1"/>
-    <col min="14564" max="14564" width="14.5" style="3" customWidth="1"/>
-    <col min="14565" max="14565" width="28.125" style="3" customWidth="1"/>
-    <col min="14566" max="14566" width="9" style="3" customWidth="1"/>
-    <col min="14567" max="14567" width="13.875" style="3" customWidth="1"/>
-    <col min="14568" max="14811" width="9" style="3"/>
-    <col min="14812" max="14812" width="5.5" style="3" customWidth="1"/>
-    <col min="14813" max="14813" width="22.125" style="3" customWidth="1"/>
-    <col min="14814" max="14814" width="14.75" style="3" customWidth="1"/>
-    <col min="14815" max="14815" width="37.75" style="3" customWidth="1"/>
-    <col min="14816" max="14816" width="10.375" style="3" customWidth="1"/>
-    <col min="14817" max="14817" width="7.125" style="3" customWidth="1"/>
-    <col min="14818" max="14818" width="5.5" style="3" customWidth="1"/>
-    <col min="14819" max="14819" width="7.625" style="3" customWidth="1"/>
-    <col min="14820" max="14820" width="14.5" style="3" customWidth="1"/>
-    <col min="14821" max="14821" width="28.125" style="3" customWidth="1"/>
-    <col min="14822" max="14822" width="9" style="3" customWidth="1"/>
-    <col min="14823" max="14823" width="13.875" style="3" customWidth="1"/>
-    <col min="14824" max="15067" width="9" style="3"/>
-    <col min="15068" max="15068" width="5.5" style="3" customWidth="1"/>
-    <col min="15069" max="15069" width="22.125" style="3" customWidth="1"/>
-    <col min="15070" max="15070" width="14.75" style="3" customWidth="1"/>
-    <col min="15071" max="15071" width="37.75" style="3" customWidth="1"/>
-    <col min="15072" max="15072" width="10.375" style="3" customWidth="1"/>
-    <col min="15073" max="15073" width="7.125" style="3" customWidth="1"/>
-    <col min="15074" max="15074" width="5.5" style="3" customWidth="1"/>
-    <col min="15075" max="15075" width="7.625" style="3" customWidth="1"/>
-    <col min="15076" max="15076" width="14.5" style="3" customWidth="1"/>
-    <col min="15077" max="15077" width="28.125" style="3" customWidth="1"/>
-    <col min="15078" max="15078" width="9" style="3" customWidth="1"/>
-    <col min="15079" max="15079" width="13.875" style="3" customWidth="1"/>
-    <col min="15080" max="15323" width="9" style="3"/>
-    <col min="15324" max="15324" width="5.5" style="3" customWidth="1"/>
-    <col min="15325" max="15325" width="22.125" style="3" customWidth="1"/>
-    <col min="15326" max="15326" width="14.75" style="3" customWidth="1"/>
-    <col min="15327" max="15327" width="37.75" style="3" customWidth="1"/>
-    <col min="15328" max="15328" width="10.375" style="3" customWidth="1"/>
-    <col min="15329" max="15329" width="7.125" style="3" customWidth="1"/>
-    <col min="15330" max="15330" width="5.5" style="3" customWidth="1"/>
-    <col min="15331" max="15331" width="7.625" style="3" customWidth="1"/>
-    <col min="15332" max="15332" width="14.5" style="3" customWidth="1"/>
-    <col min="15333" max="15333" width="28.125" style="3" customWidth="1"/>
-    <col min="15334" max="15334" width="9" style="3" customWidth="1"/>
-    <col min="15335" max="15335" width="13.875" style="3" customWidth="1"/>
-    <col min="15336" max="15579" width="9" style="3"/>
-    <col min="15580" max="15580" width="5.5" style="3" customWidth="1"/>
-    <col min="15581" max="15581" width="22.125" style="3" customWidth="1"/>
-    <col min="15582" max="15582" width="14.75" style="3" customWidth="1"/>
-    <col min="15583" max="15583" width="37.75" style="3" customWidth="1"/>
-    <col min="15584" max="15584" width="10.375" style="3" customWidth="1"/>
-    <col min="15585" max="15585" width="7.125" style="3" customWidth="1"/>
-    <col min="15586" max="15586" width="5.5" style="3" customWidth="1"/>
-    <col min="15587" max="15587" width="7.625" style="3" customWidth="1"/>
-    <col min="15588" max="15588" width="14.5" style="3" customWidth="1"/>
-    <col min="15589" max="15589" width="28.125" style="3" customWidth="1"/>
-    <col min="15590" max="15590" width="9" style="3" customWidth="1"/>
-    <col min="15591" max="15591" width="13.875" style="3" customWidth="1"/>
-    <col min="15592" max="15835" width="9" style="3"/>
-    <col min="15836" max="15836" width="5.5" style="3" customWidth="1"/>
-    <col min="15837" max="15837" width="22.125" style="3" customWidth="1"/>
-    <col min="15838" max="15838" width="14.75" style="3" customWidth="1"/>
-    <col min="15839" max="15839" width="37.75" style="3" customWidth="1"/>
-    <col min="15840" max="15840" width="10.375" style="3" customWidth="1"/>
-    <col min="15841" max="15841" width="7.125" style="3" customWidth="1"/>
-    <col min="15842" max="15842" width="5.5" style="3" customWidth="1"/>
-    <col min="15843" max="15843" width="7.625" style="3" customWidth="1"/>
-    <col min="15844" max="15844" width="14.5" style="3" customWidth="1"/>
-    <col min="15845" max="15845" width="28.125" style="3" customWidth="1"/>
-    <col min="15846" max="15846" width="9" style="3" customWidth="1"/>
-    <col min="15847" max="15847" width="13.875" style="3" customWidth="1"/>
-    <col min="15848" max="16091" width="9" style="3"/>
-    <col min="16092" max="16092" width="5.5" style="3" customWidth="1"/>
-    <col min="16093" max="16093" width="22.125" style="3" customWidth="1"/>
-    <col min="16094" max="16094" width="14.75" style="3" customWidth="1"/>
-    <col min="16095" max="16095" width="37.75" style="3" customWidth="1"/>
-    <col min="16096" max="16096" width="10.375" style="3" customWidth="1"/>
-    <col min="16097" max="16097" width="7.125" style="3" customWidth="1"/>
-    <col min="16098" max="16098" width="5.5" style="3" customWidth="1"/>
-    <col min="16099" max="16099" width="7.625" style="3" customWidth="1"/>
-    <col min="16100" max="16100" width="14.5" style="3" customWidth="1"/>
-    <col min="16101" max="16101" width="28.125" style="3" customWidth="1"/>
-    <col min="16102" max="16102" width="9" style="3" customWidth="1"/>
-    <col min="16103" max="16103" width="13.875" style="3" customWidth="1"/>
-    <col min="16104" max="16369" width="9" style="3"/>
-    <col min="16370" max="16384" width="9" style="7"/>
+    <col min="12" max="206" width="9" style="3"/>
+    <col min="207" max="207" width="5.5" style="3" customWidth="1"/>
+    <col min="208" max="208" width="22.125" style="3" customWidth="1"/>
+    <col min="209" max="209" width="14.75" style="3" customWidth="1"/>
+    <col min="210" max="210" width="37.75" style="3" customWidth="1"/>
+    <col min="211" max="211" width="10.375" style="3" customWidth="1"/>
+    <col min="212" max="212" width="7.125" style="3" customWidth="1"/>
+    <col min="213" max="213" width="5.5" style="3" customWidth="1"/>
+    <col min="214" max="214" width="7.625" style="3" customWidth="1"/>
+    <col min="215" max="215" width="14.5" style="3" customWidth="1"/>
+    <col min="216" max="216" width="28.125" style="3" customWidth="1"/>
+    <col min="217" max="217" width="9" style="3" customWidth="1"/>
+    <col min="218" max="218" width="13.875" style="3" customWidth="1"/>
+    <col min="219" max="462" width="9" style="3"/>
+    <col min="463" max="463" width="5.5" style="3" customWidth="1"/>
+    <col min="464" max="464" width="22.125" style="3" customWidth="1"/>
+    <col min="465" max="465" width="14.75" style="3" customWidth="1"/>
+    <col min="466" max="466" width="37.75" style="3" customWidth="1"/>
+    <col min="467" max="467" width="10.375" style="3" customWidth="1"/>
+    <col min="468" max="468" width="7.125" style="3" customWidth="1"/>
+    <col min="469" max="469" width="5.5" style="3" customWidth="1"/>
+    <col min="470" max="470" width="7.625" style="3" customWidth="1"/>
+    <col min="471" max="471" width="14.5" style="3" customWidth="1"/>
+    <col min="472" max="472" width="28.125" style="3" customWidth="1"/>
+    <col min="473" max="473" width="9" style="3" customWidth="1"/>
+    <col min="474" max="474" width="13.875" style="3" customWidth="1"/>
+    <col min="475" max="718" width="9" style="3"/>
+    <col min="719" max="719" width="5.5" style="3" customWidth="1"/>
+    <col min="720" max="720" width="22.125" style="3" customWidth="1"/>
+    <col min="721" max="721" width="14.75" style="3" customWidth="1"/>
+    <col min="722" max="722" width="37.75" style="3" customWidth="1"/>
+    <col min="723" max="723" width="10.375" style="3" customWidth="1"/>
+    <col min="724" max="724" width="7.125" style="3" customWidth="1"/>
+    <col min="725" max="725" width="5.5" style="3" customWidth="1"/>
+    <col min="726" max="726" width="7.625" style="3" customWidth="1"/>
+    <col min="727" max="727" width="14.5" style="3" customWidth="1"/>
+    <col min="728" max="728" width="28.125" style="3" customWidth="1"/>
+    <col min="729" max="729" width="9" style="3" customWidth="1"/>
+    <col min="730" max="730" width="13.875" style="3" customWidth="1"/>
+    <col min="731" max="974" width="9" style="3"/>
+    <col min="975" max="975" width="5.5" style="3" customWidth="1"/>
+    <col min="976" max="976" width="22.125" style="3" customWidth="1"/>
+    <col min="977" max="977" width="14.75" style="3" customWidth="1"/>
+    <col min="978" max="978" width="37.75" style="3" customWidth="1"/>
+    <col min="979" max="979" width="10.375" style="3" customWidth="1"/>
+    <col min="980" max="980" width="7.125" style="3" customWidth="1"/>
+    <col min="981" max="981" width="5.5" style="3" customWidth="1"/>
+    <col min="982" max="982" width="7.625" style="3" customWidth="1"/>
+    <col min="983" max="983" width="14.5" style="3" customWidth="1"/>
+    <col min="984" max="984" width="28.125" style="3" customWidth="1"/>
+    <col min="985" max="985" width="9" style="3" customWidth="1"/>
+    <col min="986" max="986" width="13.875" style="3" customWidth="1"/>
+    <col min="987" max="1230" width="9" style="3"/>
+    <col min="1231" max="1231" width="5.5" style="3" customWidth="1"/>
+    <col min="1232" max="1232" width="22.125" style="3" customWidth="1"/>
+    <col min="1233" max="1233" width="14.75" style="3" customWidth="1"/>
+    <col min="1234" max="1234" width="37.75" style="3" customWidth="1"/>
+    <col min="1235" max="1235" width="10.375" style="3" customWidth="1"/>
+    <col min="1236" max="1236" width="7.125" style="3" customWidth="1"/>
+    <col min="1237" max="1237" width="5.5" style="3" customWidth="1"/>
+    <col min="1238" max="1238" width="7.625" style="3" customWidth="1"/>
+    <col min="1239" max="1239" width="14.5" style="3" customWidth="1"/>
+    <col min="1240" max="1240" width="28.125" style="3" customWidth="1"/>
+    <col min="1241" max="1241" width="9" style="3" customWidth="1"/>
+    <col min="1242" max="1242" width="13.875" style="3" customWidth="1"/>
+    <col min="1243" max="1486" width="9" style="3"/>
+    <col min="1487" max="1487" width="5.5" style="3" customWidth="1"/>
+    <col min="1488" max="1488" width="22.125" style="3" customWidth="1"/>
+    <col min="1489" max="1489" width="14.75" style="3" customWidth="1"/>
+    <col min="1490" max="1490" width="37.75" style="3" customWidth="1"/>
+    <col min="1491" max="1491" width="10.375" style="3" customWidth="1"/>
+    <col min="1492" max="1492" width="7.125" style="3" customWidth="1"/>
+    <col min="1493" max="1493" width="5.5" style="3" customWidth="1"/>
+    <col min="1494" max="1494" width="7.625" style="3" customWidth="1"/>
+    <col min="1495" max="1495" width="14.5" style="3" customWidth="1"/>
+    <col min="1496" max="1496" width="28.125" style="3" customWidth="1"/>
+    <col min="1497" max="1497" width="9" style="3" customWidth="1"/>
+    <col min="1498" max="1498" width="13.875" style="3" customWidth="1"/>
+    <col min="1499" max="1742" width="9" style="3"/>
+    <col min="1743" max="1743" width="5.5" style="3" customWidth="1"/>
+    <col min="1744" max="1744" width="22.125" style="3" customWidth="1"/>
+    <col min="1745" max="1745" width="14.75" style="3" customWidth="1"/>
+    <col min="1746" max="1746" width="37.75" style="3" customWidth="1"/>
+    <col min="1747" max="1747" width="10.375" style="3" customWidth="1"/>
+    <col min="1748" max="1748" width="7.125" style="3" customWidth="1"/>
+    <col min="1749" max="1749" width="5.5" style="3" customWidth="1"/>
+    <col min="1750" max="1750" width="7.625" style="3" customWidth="1"/>
+    <col min="1751" max="1751" width="14.5" style="3" customWidth="1"/>
+    <col min="1752" max="1752" width="28.125" style="3" customWidth="1"/>
+    <col min="1753" max="1753" width="9" style="3" customWidth="1"/>
+    <col min="1754" max="1754" width="13.875" style="3" customWidth="1"/>
+    <col min="1755" max="1998" width="9" style="3"/>
+    <col min="1999" max="1999" width="5.5" style="3" customWidth="1"/>
+    <col min="2000" max="2000" width="22.125" style="3" customWidth="1"/>
+    <col min="2001" max="2001" width="14.75" style="3" customWidth="1"/>
+    <col min="2002" max="2002" width="37.75" style="3" customWidth="1"/>
+    <col min="2003" max="2003" width="10.375" style="3" customWidth="1"/>
+    <col min="2004" max="2004" width="7.125" style="3" customWidth="1"/>
+    <col min="2005" max="2005" width="5.5" style="3" customWidth="1"/>
+    <col min="2006" max="2006" width="7.625" style="3" customWidth="1"/>
+    <col min="2007" max="2007" width="14.5" style="3" customWidth="1"/>
+    <col min="2008" max="2008" width="28.125" style="3" customWidth="1"/>
+    <col min="2009" max="2009" width="9" style="3" customWidth="1"/>
+    <col min="2010" max="2010" width="13.875" style="3" customWidth="1"/>
+    <col min="2011" max="2254" width="9" style="3"/>
+    <col min="2255" max="2255" width="5.5" style="3" customWidth="1"/>
+    <col min="2256" max="2256" width="22.125" style="3" customWidth="1"/>
+    <col min="2257" max="2257" width="14.75" style="3" customWidth="1"/>
+    <col min="2258" max="2258" width="37.75" style="3" customWidth="1"/>
+    <col min="2259" max="2259" width="10.375" style="3" customWidth="1"/>
+    <col min="2260" max="2260" width="7.125" style="3" customWidth="1"/>
+    <col min="2261" max="2261" width="5.5" style="3" customWidth="1"/>
+    <col min="2262" max="2262" width="7.625" style="3" customWidth="1"/>
+    <col min="2263" max="2263" width="14.5" style="3" customWidth="1"/>
+    <col min="2264" max="2264" width="28.125" style="3" customWidth="1"/>
+    <col min="2265" max="2265" width="9" style="3" customWidth="1"/>
+    <col min="2266" max="2266" width="13.875" style="3" customWidth="1"/>
+    <col min="2267" max="2510" width="9" style="3"/>
+    <col min="2511" max="2511" width="5.5" style="3" customWidth="1"/>
+    <col min="2512" max="2512" width="22.125" style="3" customWidth="1"/>
+    <col min="2513" max="2513" width="14.75" style="3" customWidth="1"/>
+    <col min="2514" max="2514" width="37.75" style="3" customWidth="1"/>
+    <col min="2515" max="2515" width="10.375" style="3" customWidth="1"/>
+    <col min="2516" max="2516" width="7.125" style="3" customWidth="1"/>
+    <col min="2517" max="2517" width="5.5" style="3" customWidth="1"/>
+    <col min="2518" max="2518" width="7.625" style="3" customWidth="1"/>
+    <col min="2519" max="2519" width="14.5" style="3" customWidth="1"/>
+    <col min="2520" max="2520" width="28.125" style="3" customWidth="1"/>
+    <col min="2521" max="2521" width="9" style="3" customWidth="1"/>
+    <col min="2522" max="2522" width="13.875" style="3" customWidth="1"/>
+    <col min="2523" max="2766" width="9" style="3"/>
+    <col min="2767" max="2767" width="5.5" style="3" customWidth="1"/>
+    <col min="2768" max="2768" width="22.125" style="3" customWidth="1"/>
+    <col min="2769" max="2769" width="14.75" style="3" customWidth="1"/>
+    <col min="2770" max="2770" width="37.75" style="3" customWidth="1"/>
+    <col min="2771" max="2771" width="10.375" style="3" customWidth="1"/>
+    <col min="2772" max="2772" width="7.125" style="3" customWidth="1"/>
+    <col min="2773" max="2773" width="5.5" style="3" customWidth="1"/>
+    <col min="2774" max="2774" width="7.625" style="3" customWidth="1"/>
+    <col min="2775" max="2775" width="14.5" style="3" customWidth="1"/>
+    <col min="2776" max="2776" width="28.125" style="3" customWidth="1"/>
+    <col min="2777" max="2777" width="9" style="3" customWidth="1"/>
+    <col min="2778" max="2778" width="13.875" style="3" customWidth="1"/>
+    <col min="2779" max="3022" width="9" style="3"/>
+    <col min="3023" max="3023" width="5.5" style="3" customWidth="1"/>
+    <col min="3024" max="3024" width="22.125" style="3" customWidth="1"/>
+    <col min="3025" max="3025" width="14.75" style="3" customWidth="1"/>
+    <col min="3026" max="3026" width="37.75" style="3" customWidth="1"/>
+    <col min="3027" max="3027" width="10.375" style="3" customWidth="1"/>
+    <col min="3028" max="3028" width="7.125" style="3" customWidth="1"/>
+    <col min="3029" max="3029" width="5.5" style="3" customWidth="1"/>
+    <col min="3030" max="3030" width="7.625" style="3" customWidth="1"/>
+    <col min="3031" max="3031" width="14.5" style="3" customWidth="1"/>
+    <col min="3032" max="3032" width="28.125" style="3" customWidth="1"/>
+    <col min="3033" max="3033" width="9" style="3" customWidth="1"/>
+    <col min="3034" max="3034" width="13.875" style="3" customWidth="1"/>
+    <col min="3035" max="3278" width="9" style="3"/>
+    <col min="3279" max="3279" width="5.5" style="3" customWidth="1"/>
+    <col min="3280" max="3280" width="22.125" style="3" customWidth="1"/>
+    <col min="3281" max="3281" width="14.75" style="3" customWidth="1"/>
+    <col min="3282" max="3282" width="37.75" style="3" customWidth="1"/>
+    <col min="3283" max="3283" width="10.375" style="3" customWidth="1"/>
+    <col min="3284" max="3284" width="7.125" style="3" customWidth="1"/>
+    <col min="3285" max="3285" width="5.5" style="3" customWidth="1"/>
+    <col min="3286" max="3286" width="7.625" style="3" customWidth="1"/>
+    <col min="3287" max="3287" width="14.5" style="3" customWidth="1"/>
+    <col min="3288" max="3288" width="28.125" style="3" customWidth="1"/>
+    <col min="3289" max="3289" width="9" style="3" customWidth="1"/>
+    <col min="3290" max="3290" width="13.875" style="3" customWidth="1"/>
+    <col min="3291" max="3534" width="9" style="3"/>
+    <col min="3535" max="3535" width="5.5" style="3" customWidth="1"/>
+    <col min="3536" max="3536" width="22.125" style="3" customWidth="1"/>
+    <col min="3537" max="3537" width="14.75" style="3" customWidth="1"/>
+    <col min="3538" max="3538" width="37.75" style="3" customWidth="1"/>
+    <col min="3539" max="3539" width="10.375" style="3" customWidth="1"/>
+    <col min="3540" max="3540" width="7.125" style="3" customWidth="1"/>
+    <col min="3541" max="3541" width="5.5" style="3" customWidth="1"/>
+    <col min="3542" max="3542" width="7.625" style="3" customWidth="1"/>
+    <col min="3543" max="3543" width="14.5" style="3" customWidth="1"/>
+    <col min="3544" max="3544" width="28.125" style="3" customWidth="1"/>
+    <col min="3545" max="3545" width="9" style="3" customWidth="1"/>
+    <col min="3546" max="3546" width="13.875" style="3" customWidth="1"/>
+    <col min="3547" max="3790" width="9" style="3"/>
+    <col min="3791" max="3791" width="5.5" style="3" customWidth="1"/>
+    <col min="3792" max="3792" width="22.125" style="3" customWidth="1"/>
+    <col min="3793" max="3793" width="14.75" style="3" customWidth="1"/>
+    <col min="3794" max="3794" width="37.75" style="3" customWidth="1"/>
+    <col min="3795" max="3795" width="10.375" style="3" customWidth="1"/>
+    <col min="3796" max="3796" width="7.125" style="3" customWidth="1"/>
+    <col min="3797" max="3797" width="5.5" style="3" customWidth="1"/>
+    <col min="3798" max="3798" width="7.625" style="3" customWidth="1"/>
+    <col min="3799" max="3799" width="14.5" style="3" customWidth="1"/>
+    <col min="3800" max="3800" width="28.125" style="3" customWidth="1"/>
+    <col min="3801" max="3801" width="9" style="3" customWidth="1"/>
+    <col min="3802" max="3802" width="13.875" style="3" customWidth="1"/>
+    <col min="3803" max="4046" width="9" style="3"/>
+    <col min="4047" max="4047" width="5.5" style="3" customWidth="1"/>
+    <col min="4048" max="4048" width="22.125" style="3" customWidth="1"/>
+    <col min="4049" max="4049" width="14.75" style="3" customWidth="1"/>
+    <col min="4050" max="4050" width="37.75" style="3" customWidth="1"/>
+    <col min="4051" max="4051" width="10.375" style="3" customWidth="1"/>
+    <col min="4052" max="4052" width="7.125" style="3" customWidth="1"/>
+    <col min="4053" max="4053" width="5.5" style="3" customWidth="1"/>
+    <col min="4054" max="4054" width="7.625" style="3" customWidth="1"/>
+    <col min="4055" max="4055" width="14.5" style="3" customWidth="1"/>
+    <col min="4056" max="4056" width="28.125" style="3" customWidth="1"/>
+    <col min="4057" max="4057" width="9" style="3" customWidth="1"/>
+    <col min="4058" max="4058" width="13.875" style="3" customWidth="1"/>
+    <col min="4059" max="4302" width="9" style="3"/>
+    <col min="4303" max="4303" width="5.5" style="3" customWidth="1"/>
+    <col min="4304" max="4304" width="22.125" style="3" customWidth="1"/>
+    <col min="4305" max="4305" width="14.75" style="3" customWidth="1"/>
+    <col min="4306" max="4306" width="37.75" style="3" customWidth="1"/>
+    <col min="4307" max="4307" width="10.375" style="3" customWidth="1"/>
+    <col min="4308" max="4308" width="7.125" style="3" customWidth="1"/>
+    <col min="4309" max="4309" width="5.5" style="3" customWidth="1"/>
+    <col min="4310" max="4310" width="7.625" style="3" customWidth="1"/>
+    <col min="4311" max="4311" width="14.5" style="3" customWidth="1"/>
+    <col min="4312" max="4312" width="28.125" style="3" customWidth="1"/>
+    <col min="4313" max="4313" width="9" style="3" customWidth="1"/>
+    <col min="4314" max="4314" width="13.875" style="3" customWidth="1"/>
+    <col min="4315" max="4558" width="9" style="3"/>
+    <col min="4559" max="4559" width="5.5" style="3" customWidth="1"/>
+    <col min="4560" max="4560" width="22.125" style="3" customWidth="1"/>
+    <col min="4561" max="4561" width="14.75" style="3" customWidth="1"/>
+    <col min="4562" max="4562" width="37.75" style="3" customWidth="1"/>
+    <col min="4563" max="4563" width="10.375" style="3" customWidth="1"/>
+    <col min="4564" max="4564" width="7.125" style="3" customWidth="1"/>
+    <col min="4565" max="4565" width="5.5" style="3" customWidth="1"/>
+    <col min="4566" max="4566" width="7.625" style="3" customWidth="1"/>
+    <col min="4567" max="4567" width="14.5" style="3" customWidth="1"/>
+    <col min="4568" max="4568" width="28.125" style="3" customWidth="1"/>
+    <col min="4569" max="4569" width="9" style="3" customWidth="1"/>
+    <col min="4570" max="4570" width="13.875" style="3" customWidth="1"/>
+    <col min="4571" max="4814" width="9" style="3"/>
+    <col min="4815" max="4815" width="5.5" style="3" customWidth="1"/>
+    <col min="4816" max="4816" width="22.125" style="3" customWidth="1"/>
+    <col min="4817" max="4817" width="14.75" style="3" customWidth="1"/>
+    <col min="4818" max="4818" width="37.75" style="3" customWidth="1"/>
+    <col min="4819" max="4819" width="10.375" style="3" customWidth="1"/>
+    <col min="4820" max="4820" width="7.125" style="3" customWidth="1"/>
+    <col min="4821" max="4821" width="5.5" style="3" customWidth="1"/>
+    <col min="4822" max="4822" width="7.625" style="3" customWidth="1"/>
+    <col min="4823" max="4823" width="14.5" style="3" customWidth="1"/>
+    <col min="4824" max="4824" width="28.125" style="3" customWidth="1"/>
+    <col min="4825" max="4825" width="9" style="3" customWidth="1"/>
+    <col min="4826" max="4826" width="13.875" style="3" customWidth="1"/>
+    <col min="4827" max="5070" width="9" style="3"/>
+    <col min="5071" max="5071" width="5.5" style="3" customWidth="1"/>
+    <col min="5072" max="5072" width="22.125" style="3" customWidth="1"/>
+    <col min="5073" max="5073" width="14.75" style="3" customWidth="1"/>
+    <col min="5074" max="5074" width="37.75" style="3" customWidth="1"/>
+    <col min="5075" max="5075" width="10.375" style="3" customWidth="1"/>
+    <col min="5076" max="5076" width="7.125" style="3" customWidth="1"/>
+    <col min="5077" max="5077" width="5.5" style="3" customWidth="1"/>
+    <col min="5078" max="5078" width="7.625" style="3" customWidth="1"/>
+    <col min="5079" max="5079" width="14.5" style="3" customWidth="1"/>
+    <col min="5080" max="5080" width="28.125" style="3" customWidth="1"/>
+    <col min="5081" max="5081" width="9" style="3" customWidth="1"/>
+    <col min="5082" max="5082" width="13.875" style="3" customWidth="1"/>
+    <col min="5083" max="5326" width="9" style="3"/>
+    <col min="5327" max="5327" width="5.5" style="3" customWidth="1"/>
+    <col min="5328" max="5328" width="22.125" style="3" customWidth="1"/>
+    <col min="5329" max="5329" width="14.75" style="3" customWidth="1"/>
+    <col min="5330" max="5330" width="37.75" style="3" customWidth="1"/>
+    <col min="5331" max="5331" width="10.375" style="3" customWidth="1"/>
+    <col min="5332" max="5332" width="7.125" style="3" customWidth="1"/>
+    <col min="5333" max="5333" width="5.5" style="3" customWidth="1"/>
+    <col min="5334" max="5334" width="7.625" style="3" customWidth="1"/>
+    <col min="5335" max="5335" width="14.5" style="3" customWidth="1"/>
+    <col min="5336" max="5336" width="28.125" style="3" customWidth="1"/>
+    <col min="5337" max="5337" width="9" style="3" customWidth="1"/>
+    <col min="5338" max="5338" width="13.875" style="3" customWidth="1"/>
+    <col min="5339" max="5582" width="9" style="3"/>
+    <col min="5583" max="5583" width="5.5" style="3" customWidth="1"/>
+    <col min="5584" max="5584" width="22.125" style="3" customWidth="1"/>
+    <col min="5585" max="5585" width="14.75" style="3" customWidth="1"/>
+    <col min="5586" max="5586" width="37.75" style="3" customWidth="1"/>
+    <col min="5587" max="5587" width="10.375" style="3" customWidth="1"/>
+    <col min="5588" max="5588" width="7.125" style="3" customWidth="1"/>
+    <col min="5589" max="5589" width="5.5" style="3" customWidth="1"/>
+    <col min="5590" max="5590" width="7.625" style="3" customWidth="1"/>
+    <col min="5591" max="5591" width="14.5" style="3" customWidth="1"/>
+    <col min="5592" max="5592" width="28.125" style="3" customWidth="1"/>
+    <col min="5593" max="5593" width="9" style="3" customWidth="1"/>
+    <col min="5594" max="5594" width="13.875" style="3" customWidth="1"/>
+    <col min="5595" max="5838" width="9" style="3"/>
+    <col min="5839" max="5839" width="5.5" style="3" customWidth="1"/>
+    <col min="5840" max="5840" width="22.125" style="3" customWidth="1"/>
+    <col min="5841" max="5841" width="14.75" style="3" customWidth="1"/>
+    <col min="5842" max="5842" width="37.75" style="3" customWidth="1"/>
+    <col min="5843" max="5843" width="10.375" style="3" customWidth="1"/>
+    <col min="5844" max="5844" width="7.125" style="3" customWidth="1"/>
+    <col min="5845" max="5845" width="5.5" style="3" customWidth="1"/>
+    <col min="5846" max="5846" width="7.625" style="3" customWidth="1"/>
+    <col min="5847" max="5847" width="14.5" style="3" customWidth="1"/>
+    <col min="5848" max="5848" width="28.125" style="3" customWidth="1"/>
+    <col min="5849" max="5849" width="9" style="3" customWidth="1"/>
+    <col min="5850" max="5850" width="13.875" style="3" customWidth="1"/>
+    <col min="5851" max="6094" width="9" style="3"/>
+    <col min="6095" max="6095" width="5.5" style="3" customWidth="1"/>
+    <col min="6096" max="6096" width="22.125" style="3" customWidth="1"/>
+    <col min="6097" max="6097" width="14.75" style="3" customWidth="1"/>
+    <col min="6098" max="6098" width="37.75" style="3" customWidth="1"/>
+    <col min="6099" max="6099" width="10.375" style="3" customWidth="1"/>
+    <col min="6100" max="6100" width="7.125" style="3" customWidth="1"/>
+    <col min="6101" max="6101" width="5.5" style="3" customWidth="1"/>
+    <col min="6102" max="6102" width="7.625" style="3" customWidth="1"/>
+    <col min="6103" max="6103" width="14.5" style="3" customWidth="1"/>
+    <col min="6104" max="6104" width="28.125" style="3" customWidth="1"/>
+    <col min="6105" max="6105" width="9" style="3" customWidth="1"/>
+    <col min="6106" max="6106" width="13.875" style="3" customWidth="1"/>
+    <col min="6107" max="6350" width="9" style="3"/>
+    <col min="6351" max="6351" width="5.5" style="3" customWidth="1"/>
+    <col min="6352" max="6352" width="22.125" style="3" customWidth="1"/>
+    <col min="6353" max="6353" width="14.75" style="3" customWidth="1"/>
+    <col min="6354" max="6354" width="37.75" style="3" customWidth="1"/>
+    <col min="6355" max="6355" width="10.375" style="3" customWidth="1"/>
+    <col min="6356" max="6356" width="7.125" style="3" customWidth="1"/>
+    <col min="6357" max="6357" width="5.5" style="3" customWidth="1"/>
+    <col min="6358" max="6358" width="7.625" style="3" customWidth="1"/>
+    <col min="6359" max="6359" width="14.5" style="3" customWidth="1"/>
+    <col min="6360" max="6360" width="28.125" style="3" customWidth="1"/>
+    <col min="6361" max="6361" width="9" style="3" customWidth="1"/>
+    <col min="6362" max="6362" width="13.875" style="3" customWidth="1"/>
+    <col min="6363" max="6606" width="9" style="3"/>
+    <col min="6607" max="6607" width="5.5" style="3" customWidth="1"/>
+    <col min="6608" max="6608" width="22.125" style="3" customWidth="1"/>
+    <col min="6609" max="6609" width="14.75" style="3" customWidth="1"/>
+    <col min="6610" max="6610" width="37.75" style="3" customWidth="1"/>
+    <col min="6611" max="6611" width="10.375" style="3" customWidth="1"/>
+    <col min="6612" max="6612" width="7.125" style="3" customWidth="1"/>
+    <col min="6613" max="6613" width="5.5" style="3" customWidth="1"/>
+    <col min="6614" max="6614" width="7.625" style="3" customWidth="1"/>
+    <col min="6615" max="6615" width="14.5" style="3" customWidth="1"/>
+    <col min="6616" max="6616" width="28.125" style="3" customWidth="1"/>
+    <col min="6617" max="6617" width="9" style="3" customWidth="1"/>
+    <col min="6618" max="6618" width="13.875" style="3" customWidth="1"/>
+    <col min="6619" max="6862" width="9" style="3"/>
+    <col min="6863" max="6863" width="5.5" style="3" customWidth="1"/>
+    <col min="6864" max="6864" width="22.125" style="3" customWidth="1"/>
+    <col min="6865" max="6865" width="14.75" style="3" customWidth="1"/>
+    <col min="6866" max="6866" width="37.75" style="3" customWidth="1"/>
+    <col min="6867" max="6867" width="10.375" style="3" customWidth="1"/>
+    <col min="6868" max="6868" width="7.125" style="3" customWidth="1"/>
+    <col min="6869" max="6869" width="5.5" style="3" customWidth="1"/>
+    <col min="6870" max="6870" width="7.625" style="3" customWidth="1"/>
+    <col min="6871" max="6871" width="14.5" style="3" customWidth="1"/>
+    <col min="6872" max="6872" width="28.125" style="3" customWidth="1"/>
+    <col min="6873" max="6873" width="9" style="3" customWidth="1"/>
+    <col min="6874" max="6874" width="13.875" style="3" customWidth="1"/>
+    <col min="6875" max="7118" width="9" style="3"/>
+    <col min="7119" max="7119" width="5.5" style="3" customWidth="1"/>
+    <col min="7120" max="7120" width="22.125" style="3" customWidth="1"/>
+    <col min="7121" max="7121" width="14.75" style="3" customWidth="1"/>
+    <col min="7122" max="7122" width="37.75" style="3" customWidth="1"/>
+    <col min="7123" max="7123" width="10.375" style="3" customWidth="1"/>
+    <col min="7124" max="7124" width="7.125" style="3" customWidth="1"/>
+    <col min="7125" max="7125" width="5.5" style="3" customWidth="1"/>
+    <col min="7126" max="7126" width="7.625" style="3" customWidth="1"/>
+    <col min="7127" max="7127" width="14.5" style="3" customWidth="1"/>
+    <col min="7128" max="7128" width="28.125" style="3" customWidth="1"/>
+    <col min="7129" max="7129" width="9" style="3" customWidth="1"/>
+    <col min="7130" max="7130" width="13.875" style="3" customWidth="1"/>
+    <col min="7131" max="7374" width="9" style="3"/>
+    <col min="7375" max="7375" width="5.5" style="3" customWidth="1"/>
+    <col min="7376" max="7376" width="22.125" style="3" customWidth="1"/>
+    <col min="7377" max="7377" width="14.75" style="3" customWidth="1"/>
+    <col min="7378" max="7378" width="37.75" style="3" customWidth="1"/>
+    <col min="7379" max="7379" width="10.375" style="3" customWidth="1"/>
+    <col min="7380" max="7380" width="7.125" style="3" customWidth="1"/>
+    <col min="7381" max="7381" width="5.5" style="3" customWidth="1"/>
+    <col min="7382" max="7382" width="7.625" style="3" customWidth="1"/>
+    <col min="7383" max="7383" width="14.5" style="3" customWidth="1"/>
+    <col min="7384" max="7384" width="28.125" style="3" customWidth="1"/>
+    <col min="7385" max="7385" width="9" style="3" customWidth="1"/>
+    <col min="7386" max="7386" width="13.875" style="3" customWidth="1"/>
+    <col min="7387" max="7630" width="9" style="3"/>
+    <col min="7631" max="7631" width="5.5" style="3" customWidth="1"/>
+    <col min="7632" max="7632" width="22.125" style="3" customWidth="1"/>
+    <col min="7633" max="7633" width="14.75" style="3" customWidth="1"/>
+    <col min="7634" max="7634" width="37.75" style="3" customWidth="1"/>
+    <col min="7635" max="7635" width="10.375" style="3" customWidth="1"/>
+    <col min="7636" max="7636" width="7.125" style="3" customWidth="1"/>
+    <col min="7637" max="7637" width="5.5" style="3" customWidth="1"/>
+    <col min="7638" max="7638" width="7.625" style="3" customWidth="1"/>
+    <col min="7639" max="7639" width="14.5" style="3" customWidth="1"/>
+    <col min="7640" max="7640" width="28.125" style="3" customWidth="1"/>
+    <col min="7641" max="7641" width="9" style="3" customWidth="1"/>
+    <col min="7642" max="7642" width="13.875" style="3" customWidth="1"/>
+    <col min="7643" max="7886" width="9" style="3"/>
+    <col min="7887" max="7887" width="5.5" style="3" customWidth="1"/>
+    <col min="7888" max="7888" width="22.125" style="3" customWidth="1"/>
+    <col min="7889" max="7889" width="14.75" style="3" customWidth="1"/>
+    <col min="7890" max="7890" width="37.75" style="3" customWidth="1"/>
+    <col min="7891" max="7891" width="10.375" style="3" customWidth="1"/>
+    <col min="7892" max="7892" width="7.125" style="3" customWidth="1"/>
+    <col min="7893" max="7893" width="5.5" style="3" customWidth="1"/>
+    <col min="7894" max="7894" width="7.625" style="3" customWidth="1"/>
+    <col min="7895" max="7895" width="14.5" style="3" customWidth="1"/>
+    <col min="7896" max="7896" width="28.125" style="3" customWidth="1"/>
+    <col min="7897" max="7897" width="9" style="3" customWidth="1"/>
+    <col min="7898" max="7898" width="13.875" style="3" customWidth="1"/>
+    <col min="7899" max="8142" width="9" style="3"/>
+    <col min="8143" max="8143" width="5.5" style="3" customWidth="1"/>
+    <col min="8144" max="8144" width="22.125" style="3" customWidth="1"/>
+    <col min="8145" max="8145" width="14.75" style="3" customWidth="1"/>
+    <col min="8146" max="8146" width="37.75" style="3" customWidth="1"/>
+    <col min="8147" max="8147" width="10.375" style="3" customWidth="1"/>
+    <col min="8148" max="8148" width="7.125" style="3" customWidth="1"/>
+    <col min="8149" max="8149" width="5.5" style="3" customWidth="1"/>
+    <col min="8150" max="8150" width="7.625" style="3" customWidth="1"/>
+    <col min="8151" max="8151" width="14.5" style="3" customWidth="1"/>
+    <col min="8152" max="8152" width="28.125" style="3" customWidth="1"/>
+    <col min="8153" max="8153" width="9" style="3" customWidth="1"/>
+    <col min="8154" max="8154" width="13.875" style="3" customWidth="1"/>
+    <col min="8155" max="8398" width="9" style="3"/>
+    <col min="8399" max="8399" width="5.5" style="3" customWidth="1"/>
+    <col min="8400" max="8400" width="22.125" style="3" customWidth="1"/>
+    <col min="8401" max="8401" width="14.75" style="3" customWidth="1"/>
+    <col min="8402" max="8402" width="37.75" style="3" customWidth="1"/>
+    <col min="8403" max="8403" width="10.375" style="3" customWidth="1"/>
+    <col min="8404" max="8404" width="7.125" style="3" customWidth="1"/>
+    <col min="8405" max="8405" width="5.5" style="3" customWidth="1"/>
+    <col min="8406" max="8406" width="7.625" style="3" customWidth="1"/>
+    <col min="8407" max="8407" width="14.5" style="3" customWidth="1"/>
+    <col min="8408" max="8408" width="28.125" style="3" customWidth="1"/>
+    <col min="8409" max="8409" width="9" style="3" customWidth="1"/>
+    <col min="8410" max="8410" width="13.875" style="3" customWidth="1"/>
+    <col min="8411" max="8654" width="9" style="3"/>
+    <col min="8655" max="8655" width="5.5" style="3" customWidth="1"/>
+    <col min="8656" max="8656" width="22.125" style="3" customWidth="1"/>
+    <col min="8657" max="8657" width="14.75" style="3" customWidth="1"/>
+    <col min="8658" max="8658" width="37.75" style="3" customWidth="1"/>
+    <col min="8659" max="8659" width="10.375" style="3" customWidth="1"/>
+    <col min="8660" max="8660" width="7.125" style="3" customWidth="1"/>
+    <col min="8661" max="8661" width="5.5" style="3" customWidth="1"/>
+    <col min="8662" max="8662" width="7.625" style="3" customWidth="1"/>
+    <col min="8663" max="8663" width="14.5" style="3" customWidth="1"/>
+    <col min="8664" max="8664" width="28.125" style="3" customWidth="1"/>
+    <col min="8665" max="8665" width="9" style="3" customWidth="1"/>
+    <col min="8666" max="8666" width="13.875" style="3" customWidth="1"/>
+    <col min="8667" max="8910" width="9" style="3"/>
+    <col min="8911" max="8911" width="5.5" style="3" customWidth="1"/>
+    <col min="8912" max="8912" width="22.125" style="3" customWidth="1"/>
+    <col min="8913" max="8913" width="14.75" style="3" customWidth="1"/>
+    <col min="8914" max="8914" width="37.75" style="3" customWidth="1"/>
+    <col min="8915" max="8915" width="10.375" style="3" customWidth="1"/>
+    <col min="8916" max="8916" width="7.125" style="3" customWidth="1"/>
+    <col min="8917" max="8917" width="5.5" style="3" customWidth="1"/>
+    <col min="8918" max="8918" width="7.625" style="3" customWidth="1"/>
+    <col min="8919" max="8919" width="14.5" style="3" customWidth="1"/>
+    <col min="8920" max="8920" width="28.125" style="3" customWidth="1"/>
+    <col min="8921" max="8921" width="9" style="3" customWidth="1"/>
+    <col min="8922" max="8922" width="13.875" style="3" customWidth="1"/>
+    <col min="8923" max="9166" width="9" style="3"/>
+    <col min="9167" max="9167" width="5.5" style="3" customWidth="1"/>
+    <col min="9168" max="9168" width="22.125" style="3" customWidth="1"/>
+    <col min="9169" max="9169" width="14.75" style="3" customWidth="1"/>
+    <col min="9170" max="9170" width="37.75" style="3" customWidth="1"/>
+    <col min="9171" max="9171" width="10.375" style="3" customWidth="1"/>
+    <col min="9172" max="9172" width="7.125" style="3" customWidth="1"/>
+    <col min="9173" max="9173" width="5.5" style="3" customWidth="1"/>
+    <col min="9174" max="9174" width="7.625" style="3" customWidth="1"/>
+    <col min="9175" max="9175" width="14.5" style="3" customWidth="1"/>
+    <col min="9176" max="9176" width="28.125" style="3" customWidth="1"/>
+    <col min="9177" max="9177" width="9" style="3" customWidth="1"/>
+    <col min="9178" max="9178" width="13.875" style="3" customWidth="1"/>
+    <col min="9179" max="9422" width="9" style="3"/>
+    <col min="9423" max="9423" width="5.5" style="3" customWidth="1"/>
+    <col min="9424" max="9424" width="22.125" style="3" customWidth="1"/>
+    <col min="9425" max="9425" width="14.75" style="3" customWidth="1"/>
+    <col min="9426" max="9426" width="37.75" style="3" customWidth="1"/>
+    <col min="9427" max="9427" width="10.375" style="3" customWidth="1"/>
+    <col min="9428" max="9428" width="7.125" style="3" customWidth="1"/>
+    <col min="9429" max="9429" width="5.5" style="3" customWidth="1"/>
+    <col min="9430" max="9430" width="7.625" style="3" customWidth="1"/>
+    <col min="9431" max="9431" width="14.5" style="3" customWidth="1"/>
+    <col min="9432" max="9432" width="28.125" style="3" customWidth="1"/>
+    <col min="9433" max="9433" width="9" style="3" customWidth="1"/>
+    <col min="9434" max="9434" width="13.875" style="3" customWidth="1"/>
+    <col min="9435" max="9678" width="9" style="3"/>
+    <col min="9679" max="9679" width="5.5" style="3" customWidth="1"/>
+    <col min="9680" max="9680" width="22.125" style="3" customWidth="1"/>
+    <col min="9681" max="9681" width="14.75" style="3" customWidth="1"/>
+    <col min="9682" max="9682" width="37.75" style="3" customWidth="1"/>
+    <col min="9683" max="9683" width="10.375" style="3" customWidth="1"/>
+    <col min="9684" max="9684" width="7.125" style="3" customWidth="1"/>
+    <col min="9685" max="9685" width="5.5" style="3" customWidth="1"/>
+    <col min="9686" max="9686" width="7.625" style="3" customWidth="1"/>
+    <col min="9687" max="9687" width="14.5" style="3" customWidth="1"/>
+    <col min="9688" max="9688" width="28.125" style="3" customWidth="1"/>
+    <col min="9689" max="9689" width="9" style="3" customWidth="1"/>
+    <col min="9690" max="9690" width="13.875" style="3" customWidth="1"/>
+    <col min="9691" max="9934" width="9" style="3"/>
+    <col min="9935" max="9935" width="5.5" style="3" customWidth="1"/>
+    <col min="9936" max="9936" width="22.125" style="3" customWidth="1"/>
+    <col min="9937" max="9937" width="14.75" style="3" customWidth="1"/>
+    <col min="9938" max="9938" width="37.75" style="3" customWidth="1"/>
+    <col min="9939" max="9939" width="10.375" style="3" customWidth="1"/>
+    <col min="9940" max="9940" width="7.125" style="3" customWidth="1"/>
+    <col min="9941" max="9941" width="5.5" style="3" customWidth="1"/>
+    <col min="9942" max="9942" width="7.625" style="3" customWidth="1"/>
+    <col min="9943" max="9943" width="14.5" style="3" customWidth="1"/>
+    <col min="9944" max="9944" width="28.125" style="3" customWidth="1"/>
+    <col min="9945" max="9945" width="9" style="3" customWidth="1"/>
+    <col min="9946" max="9946" width="13.875" style="3" customWidth="1"/>
+    <col min="9947" max="10190" width="9" style="3"/>
+    <col min="10191" max="10191" width="5.5" style="3" customWidth="1"/>
+    <col min="10192" max="10192" width="22.125" style="3" customWidth="1"/>
+    <col min="10193" max="10193" width="14.75" style="3" customWidth="1"/>
+    <col min="10194" max="10194" width="37.75" style="3" customWidth="1"/>
+    <col min="10195" max="10195" width="10.375" style="3" customWidth="1"/>
+    <col min="10196" max="10196" width="7.125" style="3" customWidth="1"/>
+    <col min="10197" max="10197" width="5.5" style="3" customWidth="1"/>
+    <col min="10198" max="10198" width="7.625" style="3" customWidth="1"/>
+    <col min="10199" max="10199" width="14.5" style="3" customWidth="1"/>
+    <col min="10200" max="10200" width="28.125" style="3" customWidth="1"/>
+    <col min="10201" max="10201" width="9" style="3" customWidth="1"/>
+    <col min="10202" max="10202" width="13.875" style="3" customWidth="1"/>
+    <col min="10203" max="10446" width="9" style="3"/>
+    <col min="10447" max="10447" width="5.5" style="3" customWidth="1"/>
+    <col min="10448" max="10448" width="22.125" style="3" customWidth="1"/>
+    <col min="10449" max="10449" width="14.75" style="3" customWidth="1"/>
+    <col min="10450" max="10450" width="37.75" style="3" customWidth="1"/>
+    <col min="10451" max="10451" width="10.375" style="3" customWidth="1"/>
+    <col min="10452" max="10452" width="7.125" style="3" customWidth="1"/>
+    <col min="10453" max="10453" width="5.5" style="3" customWidth="1"/>
+    <col min="10454" max="10454" width="7.625" style="3" customWidth="1"/>
+    <col min="10455" max="10455" width="14.5" style="3" customWidth="1"/>
+    <col min="10456" max="10456" width="28.125" style="3" customWidth="1"/>
+    <col min="10457" max="10457" width="9" style="3" customWidth="1"/>
+    <col min="10458" max="10458" width="13.875" style="3" customWidth="1"/>
+    <col min="10459" max="10702" width="9" style="3"/>
+    <col min="10703" max="10703" width="5.5" style="3" customWidth="1"/>
+    <col min="10704" max="10704" width="22.125" style="3" customWidth="1"/>
+    <col min="10705" max="10705" width="14.75" style="3" customWidth="1"/>
+    <col min="10706" max="10706" width="37.75" style="3" customWidth="1"/>
+    <col min="10707" max="10707" width="10.375" style="3" customWidth="1"/>
+    <col min="10708" max="10708" width="7.125" style="3" customWidth="1"/>
+    <col min="10709" max="10709" width="5.5" style="3" customWidth="1"/>
+    <col min="10710" max="10710" width="7.625" style="3" customWidth="1"/>
+    <col min="10711" max="10711" width="14.5" style="3" customWidth="1"/>
+    <col min="10712" max="10712" width="28.125" style="3" customWidth="1"/>
+    <col min="10713" max="10713" width="9" style="3" customWidth="1"/>
+    <col min="10714" max="10714" width="13.875" style="3" customWidth="1"/>
+    <col min="10715" max="10958" width="9" style="3"/>
+    <col min="10959" max="10959" width="5.5" style="3" customWidth="1"/>
+    <col min="10960" max="10960" width="22.125" style="3" customWidth="1"/>
+    <col min="10961" max="10961" width="14.75" style="3" customWidth="1"/>
+    <col min="10962" max="10962" width="37.75" style="3" customWidth="1"/>
+    <col min="10963" max="10963" width="10.375" style="3" customWidth="1"/>
+    <col min="10964" max="10964" width="7.125" style="3" customWidth="1"/>
+    <col min="10965" max="10965" width="5.5" style="3" customWidth="1"/>
+    <col min="10966" max="10966" width="7.625" style="3" customWidth="1"/>
+    <col min="10967" max="10967" width="14.5" style="3" customWidth="1"/>
+    <col min="10968" max="10968" width="28.125" style="3" customWidth="1"/>
+    <col min="10969" max="10969" width="9" style="3" customWidth="1"/>
+    <col min="10970" max="10970" width="13.875" style="3" customWidth="1"/>
+    <col min="10971" max="11214" width="9" style="3"/>
+    <col min="11215" max="11215" width="5.5" style="3" customWidth="1"/>
+    <col min="11216" max="11216" width="22.125" style="3" customWidth="1"/>
+    <col min="11217" max="11217" width="14.75" style="3" customWidth="1"/>
+    <col min="11218" max="11218" width="37.75" style="3" customWidth="1"/>
+    <col min="11219" max="11219" width="10.375" style="3" customWidth="1"/>
+    <col min="11220" max="11220" width="7.125" style="3" customWidth="1"/>
+    <col min="11221" max="11221" width="5.5" style="3" customWidth="1"/>
+    <col min="11222" max="11222" width="7.625" style="3" customWidth="1"/>
+    <col min="11223" max="11223" width="14.5" style="3" customWidth="1"/>
+    <col min="11224" max="11224" width="28.125" style="3" customWidth="1"/>
+    <col min="11225" max="11225" width="9" style="3" customWidth="1"/>
+    <col min="11226" max="11226" width="13.875" style="3" customWidth="1"/>
+    <col min="11227" max="11470" width="9" style="3"/>
+    <col min="11471" max="11471" width="5.5" style="3" customWidth="1"/>
+    <col min="11472" max="11472" width="22.125" style="3" customWidth="1"/>
+    <col min="11473" max="11473" width="14.75" style="3" customWidth="1"/>
+    <col min="11474" max="11474" width="37.75" style="3" customWidth="1"/>
+    <col min="11475" max="11475" width="10.375" style="3" customWidth="1"/>
+    <col min="11476" max="11476" width="7.125" style="3" customWidth="1"/>
+    <col min="11477" max="11477" width="5.5" style="3" customWidth="1"/>
+    <col min="11478" max="11478" width="7.625" style="3" customWidth="1"/>
+    <col min="11479" max="11479" width="14.5" style="3" customWidth="1"/>
+    <col min="11480" max="11480" width="28.125" style="3" customWidth="1"/>
+    <col min="11481" max="11481" width="9" style="3" customWidth="1"/>
+    <col min="11482" max="11482" width="13.875" style="3" customWidth="1"/>
+    <col min="11483" max="11726" width="9" style="3"/>
+    <col min="11727" max="11727" width="5.5" style="3" customWidth="1"/>
+    <col min="11728" max="11728" width="22.125" style="3" customWidth="1"/>
+    <col min="11729" max="11729" width="14.75" style="3" customWidth="1"/>
+    <col min="11730" max="11730" width="37.75" style="3" customWidth="1"/>
+    <col min="11731" max="11731" width="10.375" style="3" customWidth="1"/>
+    <col min="11732" max="11732" width="7.125" style="3" customWidth="1"/>
+    <col min="11733" max="11733" width="5.5" style="3" customWidth="1"/>
+    <col min="11734" max="11734" width="7.625" style="3" customWidth="1"/>
+    <col min="11735" max="11735" width="14.5" style="3" customWidth="1"/>
+    <col min="11736" max="11736" width="28.125" style="3" customWidth="1"/>
+    <col min="11737" max="11737" width="9" style="3" customWidth="1"/>
+    <col min="11738" max="11738" width="13.875" style="3" customWidth="1"/>
+    <col min="11739" max="11982" width="9" style="3"/>
+    <col min="11983" max="11983" width="5.5" style="3" customWidth="1"/>
+    <col min="11984" max="11984" width="22.125" style="3" customWidth="1"/>
+    <col min="11985" max="11985" width="14.75" style="3" customWidth="1"/>
+    <col min="11986" max="11986" width="37.75" style="3" customWidth="1"/>
+    <col min="11987" max="11987" width="10.375" style="3" customWidth="1"/>
+    <col min="11988" max="11988" width="7.125" style="3" customWidth="1"/>
+    <col min="11989" max="11989" width="5.5" style="3" customWidth="1"/>
+    <col min="11990" max="11990" width="7.625" style="3" customWidth="1"/>
+    <col min="11991" max="11991" width="14.5" style="3" customWidth="1"/>
+    <col min="11992" max="11992" width="28.125" style="3" customWidth="1"/>
+    <col min="11993" max="11993" width="9" style="3" customWidth="1"/>
+    <col min="11994" max="11994" width="13.875" style="3" customWidth="1"/>
+    <col min="11995" max="12238" width="9" style="3"/>
+    <col min="12239" max="12239" width="5.5" style="3" customWidth="1"/>
+    <col min="12240" max="12240" width="22.125" style="3" customWidth="1"/>
+    <col min="12241" max="12241" width="14.75" style="3" customWidth="1"/>
+    <col min="12242" max="12242" width="37.75" style="3" customWidth="1"/>
+    <col min="12243" max="12243" width="10.375" style="3" customWidth="1"/>
+    <col min="12244" max="12244" width="7.125" style="3" customWidth="1"/>
+    <col min="12245" max="12245" width="5.5" style="3" customWidth="1"/>
+    <col min="12246" max="12246" width="7.625" style="3" customWidth="1"/>
+    <col min="12247" max="12247" width="14.5" style="3" customWidth="1"/>
+    <col min="12248" max="12248" width="28.125" style="3" customWidth="1"/>
+    <col min="12249" max="12249" width="9" style="3" customWidth="1"/>
+    <col min="12250" max="12250" width="13.875" style="3" customWidth="1"/>
+    <col min="12251" max="12494" width="9" style="3"/>
+    <col min="12495" max="12495" width="5.5" style="3" customWidth="1"/>
+    <col min="12496" max="12496" width="22.125" style="3" customWidth="1"/>
+    <col min="12497" max="12497" width="14.75" style="3" customWidth="1"/>
+    <col min="12498" max="12498" width="37.75" style="3" customWidth="1"/>
+    <col min="12499" max="12499" width="10.375" style="3" customWidth="1"/>
+    <col min="12500" max="12500" width="7.125" style="3" customWidth="1"/>
+    <col min="12501" max="12501" width="5.5" style="3" customWidth="1"/>
+    <col min="12502" max="12502" width="7.625" style="3" customWidth="1"/>
+    <col min="12503" max="12503" width="14.5" style="3" customWidth="1"/>
+    <col min="12504" max="12504" width="28.125" style="3" customWidth="1"/>
+    <col min="12505" max="12505" width="9" style="3" customWidth="1"/>
+    <col min="12506" max="12506" width="13.875" style="3" customWidth="1"/>
+    <col min="12507" max="12750" width="9" style="3"/>
+    <col min="12751" max="12751" width="5.5" style="3" customWidth="1"/>
+    <col min="12752" max="12752" width="22.125" style="3" customWidth="1"/>
+    <col min="12753" max="12753" width="14.75" style="3" customWidth="1"/>
+    <col min="12754" max="12754" width="37.75" style="3" customWidth="1"/>
+    <col min="12755" max="12755" width="10.375" style="3" customWidth="1"/>
+    <col min="12756" max="12756" width="7.125" style="3" customWidth="1"/>
+    <col min="12757" max="12757" width="5.5" style="3" customWidth="1"/>
+    <col min="12758" max="12758" width="7.625" style="3" customWidth="1"/>
+    <col min="12759" max="12759" width="14.5" style="3" customWidth="1"/>
+    <col min="12760" max="12760" width="28.125" style="3" customWidth="1"/>
+    <col min="12761" max="12761" width="9" style="3" customWidth="1"/>
+    <col min="12762" max="12762" width="13.875" style="3" customWidth="1"/>
+    <col min="12763" max="13006" width="9" style="3"/>
+    <col min="13007" max="13007" width="5.5" style="3" customWidth="1"/>
+    <col min="13008" max="13008" width="22.125" style="3" customWidth="1"/>
+    <col min="13009" max="13009" width="14.75" style="3" customWidth="1"/>
+    <col min="13010" max="13010" width="37.75" style="3" customWidth="1"/>
+    <col min="13011" max="13011" width="10.375" style="3" customWidth="1"/>
+    <col min="13012" max="13012" width="7.125" style="3" customWidth="1"/>
+    <col min="13013" max="13013" width="5.5" style="3" customWidth="1"/>
+    <col min="13014" max="13014" width="7.625" style="3" customWidth="1"/>
+    <col min="13015" max="13015" width="14.5" style="3" customWidth="1"/>
+    <col min="13016" max="13016" width="28.125" style="3" customWidth="1"/>
+    <col min="13017" max="13017" width="9" style="3" customWidth="1"/>
+    <col min="13018" max="13018" width="13.875" style="3" customWidth="1"/>
+    <col min="13019" max="13262" width="9" style="3"/>
+    <col min="13263" max="13263" width="5.5" style="3" customWidth="1"/>
+    <col min="13264" max="13264" width="22.125" style="3" customWidth="1"/>
+    <col min="13265" max="13265" width="14.75" style="3" customWidth="1"/>
+    <col min="13266" max="13266" width="37.75" style="3" customWidth="1"/>
+    <col min="13267" max="13267" width="10.375" style="3" customWidth="1"/>
+    <col min="13268" max="13268" width="7.125" style="3" customWidth="1"/>
+    <col min="13269" max="13269" width="5.5" style="3" customWidth="1"/>
+    <col min="13270" max="13270" width="7.625" style="3" customWidth="1"/>
+    <col min="13271" max="13271" width="14.5" style="3" customWidth="1"/>
+    <col min="13272" max="13272" width="28.125" style="3" customWidth="1"/>
+    <col min="13273" max="13273" width="9" style="3" customWidth="1"/>
+    <col min="13274" max="13274" width="13.875" style="3" customWidth="1"/>
+    <col min="13275" max="13518" width="9" style="3"/>
+    <col min="13519" max="13519" width="5.5" style="3" customWidth="1"/>
+    <col min="13520" max="13520" width="22.125" style="3" customWidth="1"/>
+    <col min="13521" max="13521" width="14.75" style="3" customWidth="1"/>
+    <col min="13522" max="13522" width="37.75" style="3" customWidth="1"/>
+    <col min="13523" max="13523" width="10.375" style="3" customWidth="1"/>
+    <col min="13524" max="13524" width="7.125" style="3" customWidth="1"/>
+    <col min="13525" max="13525" width="5.5" style="3" customWidth="1"/>
+    <col min="13526" max="13526" width="7.625" style="3" customWidth="1"/>
+    <col min="13527" max="13527" width="14.5" style="3" customWidth="1"/>
+    <col min="13528" max="13528" width="28.125" style="3" customWidth="1"/>
+    <col min="13529" max="13529" width="9" style="3" customWidth="1"/>
+    <col min="13530" max="13530" width="13.875" style="3" customWidth="1"/>
+    <col min="13531" max="13774" width="9" style="3"/>
+    <col min="13775" max="13775" width="5.5" style="3" customWidth="1"/>
+    <col min="13776" max="13776" width="22.125" style="3" customWidth="1"/>
+    <col min="13777" max="13777" width="14.75" style="3" customWidth="1"/>
+    <col min="13778" max="13778" width="37.75" style="3" customWidth="1"/>
+    <col min="13779" max="13779" width="10.375" style="3" customWidth="1"/>
+    <col min="13780" max="13780" width="7.125" style="3" customWidth="1"/>
+    <col min="13781" max="13781" width="5.5" style="3" customWidth="1"/>
+    <col min="13782" max="13782" width="7.625" style="3" customWidth="1"/>
+    <col min="13783" max="13783" width="14.5" style="3" customWidth="1"/>
+    <col min="13784" max="13784" width="28.125" style="3" customWidth="1"/>
+    <col min="13785" max="13785" width="9" style="3" customWidth="1"/>
+    <col min="13786" max="13786" width="13.875" style="3" customWidth="1"/>
+    <col min="13787" max="14030" width="9" style="3"/>
+    <col min="14031" max="14031" width="5.5" style="3" customWidth="1"/>
+    <col min="14032" max="14032" width="22.125" style="3" customWidth="1"/>
+    <col min="14033" max="14033" width="14.75" style="3" customWidth="1"/>
+    <col min="14034" max="14034" width="37.75" style="3" customWidth="1"/>
+    <col min="14035" max="14035" width="10.375" style="3" customWidth="1"/>
+    <col min="14036" max="14036" width="7.125" style="3" customWidth="1"/>
+    <col min="14037" max="14037" width="5.5" style="3" customWidth="1"/>
+    <col min="14038" max="14038" width="7.625" style="3" customWidth="1"/>
+    <col min="14039" max="14039" width="14.5" style="3" customWidth="1"/>
+    <col min="14040" max="14040" width="28.125" style="3" customWidth="1"/>
+    <col min="14041" max="14041" width="9" style="3" customWidth="1"/>
+    <col min="14042" max="14042" width="13.875" style="3" customWidth="1"/>
+    <col min="14043" max="14286" width="9" style="3"/>
+    <col min="14287" max="14287" width="5.5" style="3" customWidth="1"/>
+    <col min="14288" max="14288" width="22.125" style="3" customWidth="1"/>
+    <col min="14289" max="14289" width="14.75" style="3" customWidth="1"/>
+    <col min="14290" max="14290" width="37.75" style="3" customWidth="1"/>
+    <col min="14291" max="14291" width="10.375" style="3" customWidth="1"/>
+    <col min="14292" max="14292" width="7.125" style="3" customWidth="1"/>
+    <col min="14293" max="14293" width="5.5" style="3" customWidth="1"/>
+    <col min="14294" max="14294" width="7.625" style="3" customWidth="1"/>
+    <col min="14295" max="14295" width="14.5" style="3" customWidth="1"/>
+    <col min="14296" max="14296" width="28.125" style="3" customWidth="1"/>
+    <col min="14297" max="14297" width="9" style="3" customWidth="1"/>
+    <col min="14298" max="14298" width="13.875" style="3" customWidth="1"/>
+    <col min="14299" max="14542" width="9" style="3"/>
+    <col min="14543" max="14543" width="5.5" style="3" customWidth="1"/>
+    <col min="14544" max="14544" width="22.125" style="3" customWidth="1"/>
+    <col min="14545" max="14545" width="14.75" style="3" customWidth="1"/>
+    <col min="14546" max="14546" width="37.75" style="3" customWidth="1"/>
+    <col min="14547" max="14547" width="10.375" style="3" customWidth="1"/>
+    <col min="14548" max="14548" width="7.125" style="3" customWidth="1"/>
+    <col min="14549" max="14549" width="5.5" style="3" customWidth="1"/>
+    <col min="14550" max="14550" width="7.625" style="3" customWidth="1"/>
+    <col min="14551" max="14551" width="14.5" style="3" customWidth="1"/>
+    <col min="14552" max="14552" width="28.125" style="3" customWidth="1"/>
+    <col min="14553" max="14553" width="9" style="3" customWidth="1"/>
+    <col min="14554" max="14554" width="13.875" style="3" customWidth="1"/>
+    <col min="14555" max="14798" width="9" style="3"/>
+    <col min="14799" max="14799" width="5.5" style="3" customWidth="1"/>
+    <col min="14800" max="14800" width="22.125" style="3" customWidth="1"/>
+    <col min="14801" max="14801" width="14.75" style="3" customWidth="1"/>
+    <col min="14802" max="14802" width="37.75" style="3" customWidth="1"/>
+    <col min="14803" max="14803" width="10.375" style="3" customWidth="1"/>
+    <col min="14804" max="14804" width="7.125" style="3" customWidth="1"/>
+    <col min="14805" max="14805" width="5.5" style="3" customWidth="1"/>
+    <col min="14806" max="14806" width="7.625" style="3" customWidth="1"/>
+    <col min="14807" max="14807" width="14.5" style="3" customWidth="1"/>
+    <col min="14808" max="14808" width="28.125" style="3" customWidth="1"/>
+    <col min="14809" max="14809" width="9" style="3" customWidth="1"/>
+    <col min="14810" max="14810" width="13.875" style="3" customWidth="1"/>
+    <col min="14811" max="15054" width="9" style="3"/>
+    <col min="15055" max="15055" width="5.5" style="3" customWidth="1"/>
+    <col min="15056" max="15056" width="22.125" style="3" customWidth="1"/>
+    <col min="15057" max="15057" width="14.75" style="3" customWidth="1"/>
+    <col min="15058" max="15058" width="37.75" style="3" customWidth="1"/>
+    <col min="15059" max="15059" width="10.375" style="3" customWidth="1"/>
+    <col min="15060" max="15060" width="7.125" style="3" customWidth="1"/>
+    <col min="15061" max="15061" width="5.5" style="3" customWidth="1"/>
+    <col min="15062" max="15062" width="7.625" style="3" customWidth="1"/>
+    <col min="15063" max="15063" width="14.5" style="3" customWidth="1"/>
+    <col min="15064" max="15064" width="28.125" style="3" customWidth="1"/>
+    <col min="15065" max="15065" width="9" style="3" customWidth="1"/>
+    <col min="15066" max="15066" width="13.875" style="3" customWidth="1"/>
+    <col min="15067" max="15310" width="9" style="3"/>
+    <col min="15311" max="15311" width="5.5" style="3" customWidth="1"/>
+    <col min="15312" max="15312" width="22.125" style="3" customWidth="1"/>
+    <col min="15313" max="15313" width="14.75" style="3" customWidth="1"/>
+    <col min="15314" max="15314" width="37.75" style="3" customWidth="1"/>
+    <col min="15315" max="15315" width="10.375" style="3" customWidth="1"/>
+    <col min="15316" max="15316" width="7.125" style="3" customWidth="1"/>
+    <col min="15317" max="15317" width="5.5" style="3" customWidth="1"/>
+    <col min="15318" max="15318" width="7.625" style="3" customWidth="1"/>
+    <col min="15319" max="15319" width="14.5" style="3" customWidth="1"/>
+    <col min="15320" max="15320" width="28.125" style="3" customWidth="1"/>
+    <col min="15321" max="15321" width="9" style="3" customWidth="1"/>
+    <col min="15322" max="15322" width="13.875" style="3" customWidth="1"/>
+    <col min="15323" max="15566" width="9" style="3"/>
+    <col min="15567" max="15567" width="5.5" style="3" customWidth="1"/>
+    <col min="15568" max="15568" width="22.125" style="3" customWidth="1"/>
+    <col min="15569" max="15569" width="14.75" style="3" customWidth="1"/>
+    <col min="15570" max="15570" width="37.75" style="3" customWidth="1"/>
+    <col min="15571" max="15571" width="10.375" style="3" customWidth="1"/>
+    <col min="15572" max="15572" width="7.125" style="3" customWidth="1"/>
+    <col min="15573" max="15573" width="5.5" style="3" customWidth="1"/>
+    <col min="15574" max="15574" width="7.625" style="3" customWidth="1"/>
+    <col min="15575" max="15575" width="14.5" style="3" customWidth="1"/>
+    <col min="15576" max="15576" width="28.125" style="3" customWidth="1"/>
+    <col min="15577" max="15577" width="9" style="3" customWidth="1"/>
+    <col min="15578" max="15578" width="13.875" style="3" customWidth="1"/>
+    <col min="15579" max="15822" width="9" style="3"/>
+    <col min="15823" max="15823" width="5.5" style="3" customWidth="1"/>
+    <col min="15824" max="15824" width="22.125" style="3" customWidth="1"/>
+    <col min="15825" max="15825" width="14.75" style="3" customWidth="1"/>
+    <col min="15826" max="15826" width="37.75" style="3" customWidth="1"/>
+    <col min="15827" max="15827" width="10.375" style="3" customWidth="1"/>
+    <col min="15828" max="15828" width="7.125" style="3" customWidth="1"/>
+    <col min="15829" max="15829" width="5.5" style="3" customWidth="1"/>
+    <col min="15830" max="15830" width="7.625" style="3" customWidth="1"/>
+    <col min="15831" max="15831" width="14.5" style="3" customWidth="1"/>
+    <col min="15832" max="15832" width="28.125" style="3" customWidth="1"/>
+    <col min="15833" max="15833" width="9" style="3" customWidth="1"/>
+    <col min="15834" max="15834" width="13.875" style="3" customWidth="1"/>
+    <col min="15835" max="16078" width="9" style="3"/>
+    <col min="16079" max="16079" width="5.5" style="3" customWidth="1"/>
+    <col min="16080" max="16080" width="22.125" style="3" customWidth="1"/>
+    <col min="16081" max="16081" width="14.75" style="3" customWidth="1"/>
+    <col min="16082" max="16082" width="37.75" style="3" customWidth="1"/>
+    <col min="16083" max="16083" width="10.375" style="3" customWidth="1"/>
+    <col min="16084" max="16084" width="7.125" style="3" customWidth="1"/>
+    <col min="16085" max="16085" width="5.5" style="3" customWidth="1"/>
+    <col min="16086" max="16086" width="7.625" style="3" customWidth="1"/>
+    <col min="16087" max="16087" width="14.5" style="3" customWidth="1"/>
+    <col min="16088" max="16088" width="28.125" style="3" customWidth="1"/>
+    <col min="16089" max="16089" width="9" style="3" customWidth="1"/>
+    <col min="16090" max="16090" width="13.875" style="3" customWidth="1"/>
+    <col min="16091" max="16356" width="9" style="3"/>
+    <col min="16357" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:10">
@@ -8975,7 +9002,7 @@
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
-      <c r="J1" s="39"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A2" s="10"/>
@@ -9002,7 +9029,7 @@
       <c r="I2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="40"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A3" s="18"/>
@@ -9029,7 +9056,7 @@
       <c r="I3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="41"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A4" s="18"/>
@@ -9055,7 +9082,7 @@
       <c r="I4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A5" s="20" t="s">
@@ -9085,13 +9112,13 @@
       <c r="I5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="44" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A6" s="22" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
@@ -9101,20 +9128,20 @@
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="44"/>
-    </row>
-    <row r="7" ht="43" customHeight="1" spans="1:10">
+      <c r="J6" s="45"/>
+    </row>
+    <row r="7" ht="43" customHeight="1" spans="1:13">
       <c r="A7" s="24">
         <v>1</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>32</v>
@@ -9126,205 +9153,216 @@
         <v>34</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I7" s="28" t="e">
-        <f t="shared" ref="I7:I11" si="0">F7*H7</f>
+        <f>F7*H7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J7" s="45"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:10">
+      <c r="J7" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" ht="57" customHeight="1" spans="1:12">
       <c r="A8" s="24">
         <v>2</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I8" s="28" t="e">
-        <f t="shared" si="0"/>
+        <f>F8*H8</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J8" s="45"/>
-    </row>
-    <row r="9" ht="57" customHeight="1" spans="1:10">
+      <c r="J8" s="47"/>
+      <c r="L8" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" ht="42.75" spans="1:12">
       <c r="A9" s="24">
         <v>3</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>32</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I9" s="28" t="e">
-        <f t="shared" si="0"/>
+        <f>F9*H9</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J9" s="46"/>
-    </row>
-    <row r="10" ht="42.75" spans="1:10">
+      <c r="J9" s="48"/>
+      <c r="L9" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="36" spans="1:12">
       <c r="A10" s="24">
         <v>4</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>50</v>
+        <v>136</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>33</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="H10" s="28">
+        <v>420</v>
       </c>
       <c r="I10" s="28" t="e">
-        <f t="shared" si="0"/>
+        <f>F10*H10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J10" s="47"/>
-    </row>
-    <row r="11" customFormat="1" ht="28.5" spans="1:10">
+      <c r="J10" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="L10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="42.75" spans="1:13">
       <c r="A11" s="24">
         <v>5</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>56</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="28">
-        <v>360</v>
+        <v>51</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>57</v>
       </c>
       <c r="I11" s="28" t="e">
-        <f t="shared" si="0"/>
+        <f>F11*H11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J11" s="47"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="42.75" spans="1:10">
+      <c r="J11" s="49"/>
+      <c r="L11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="57" spans="1:12">
       <c r="A12" s="24">
         <v>6</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="27" t="s">
-        <v>56</v>
+      <c r="F12" s="27">
+        <v>1</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="28" t="e">
-        <f t="shared" ref="I12:I25" si="1">F12*H12</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J12" s="48"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="57" spans="1:10">
-      <c r="A13" s="24">
-        <v>7</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="27">
-        <v>1</v>
-      </c>
-      <c r="G13" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H12" s="28">
         <v>0</v>
       </c>
-      <c r="I13" s="28">
-        <f t="shared" si="1"/>
+      <c r="I12" s="28">
+        <f>F12*H12</f>
         <v>0</v>
       </c>
-      <c r="J13" s="49" t="s">
+      <c r="J12" s="50" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="14" ht="42.75" spans="1:10">
+      <c r="L12" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A13" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="45"/>
+    </row>
+    <row r="14" ht="42.75" spans="1:12">
       <c r="A14" s="24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>63</v>
@@ -9332,10 +9370,10 @@
       <c r="C14" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="31" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="27">
@@ -9348,183 +9386,175 @@
         <v>66</v>
       </c>
       <c r="I14" s="28" t="e">
-        <f t="shared" si="1"/>
+        <f>F14*H14</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J14" s="50"/>
-    </row>
-    <row r="15" ht="42.75" spans="1:10">
+      <c r="J14" s="51"/>
+      <c r="L14" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1" spans="1:14">
       <c r="A15" s="24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>69</v>
+        <v>39</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>144</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>33</v>
+      <c r="F15" s="28" t="e">
+        <f>ROUND(#REF!/20,0)</f>
+        <v>#REF!</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>70</v>
+        <v>61</v>
+      </c>
+      <c r="H15" s="28">
+        <v>2800</v>
       </c>
       <c r="I15" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J15" s="48"/>
-    </row>
-    <row r="16" ht="14.25" spans="1:10">
-      <c r="A16" s="24">
-        <v>10</v>
+        <f>F15*H15</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J15" s="51"/>
+      <c r="L15" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" ht="17.25" spans="1:13">
+      <c r="A16" s="27">
+        <v>7</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C16" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="29" t="s">
-        <v>131</v>
+      <c r="D16" s="30" t="s">
+        <v>147</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>34</v>
+      <c r="F16" s="28" t="e">
+        <f>ROUND(#REF!/70,0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="H16" s="28">
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="I16" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J16" s="50"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:10">
-      <c r="A17" s="24">
-        <v>11</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>132</v>
+        <f>F16*H16</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J16" s="51"/>
+      <c r="M16" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" ht="17.25" spans="1:13">
+      <c r="A17" s="27">
+        <v>8</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>149</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="29" t="s">
-        <v>133</v>
+      <c r="D17" s="30" t="s">
+        <v>150</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>33</v>
+      <c r="F17" s="27">
+        <v>1</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="28">
-        <v>100</v>
-      </c>
-      <c r="I17" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J17" s="50"/>
-    </row>
-    <row r="18" ht="14.25" spans="1:10">
-      <c r="A18" s="24">
-        <v>12</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="28" t="e">
-        <f>ROUND(F17/20,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G18" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="28">
-        <v>2800</v>
-      </c>
-      <c r="I18" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J18" s="50"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:10">
-      <c r="A19" s="24">
-        <v>13</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>136</v>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="51"/>
+      <c r="M17" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A18" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="45"/>
+    </row>
+    <row r="19" ht="17.25" spans="1:12">
+      <c r="A19" s="27">
+        <v>9</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>153</v>
       </c>
       <c r="C19" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="29" t="s">
-        <v>137</v>
-      </c>
+      <c r="D19" s="30"/>
       <c r="E19" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28" t="e">
+        <f>F19*H19</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J19" s="52"/>
+      <c r="L19" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" ht="42.75" spans="1:12">
+      <c r="A20" s="24">
+        <v>10</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="27" t="s">
         <v>39</v>
-      </c>
-      <c r="F19" s="28" t="e">
-        <f>ROUND(F17/70,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="28">
-        <v>4000</v>
-      </c>
-      <c r="I19" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J19" s="50"/>
-    </row>
-    <row r="20" ht="28.5" spans="1:10">
-      <c r="A20" s="24">
-        <v>14</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>130</v>
       </c>
       <c r="F20" s="28" t="s">
         <v>33</v>
@@ -9532,206 +9562,52 @@
       <c r="G20" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="28">
-        <v>50</v>
+      <c r="H20" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="I20" s="28" t="e">
-        <f t="shared" si="1"/>
+        <f>F20*H20</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J20" s="50"/>
-    </row>
-    <row r="21" ht="14.25" spans="1:10">
-      <c r="A21" s="24">
-        <v>15</v>
-      </c>
-      <c r="B21" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" s="28">
-        <v>300</v>
-      </c>
-      <c r="I21" s="28" t="e">
-        <f t="shared" si="1"/>
+      <c r="J20" s="49"/>
+      <c r="L20" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="33"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="53" t="e">
+        <f>SUM(I7:I20)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J21" s="50"/>
-    </row>
-    <row r="22" ht="14.25" spans="1:10">
-      <c r="A22" s="24">
-        <v>16</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="28">
-        <v>200</v>
-      </c>
-      <c r="I22" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J22" s="50"/>
-    </row>
-    <row r="23" ht="14.25" spans="1:10">
-      <c r="A23" s="24">
-        <v>17</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="28">
-        <v>50</v>
-      </c>
-      <c r="I23" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J23" s="50"/>
-    </row>
-    <row r="24" ht="14.25" spans="1:10">
-      <c r="A24" s="24">
-        <v>18</v>
-      </c>
-      <c r="B24" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="28">
-        <v>20</v>
-      </c>
-      <c r="I24" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J24" s="50"/>
-    </row>
-    <row r="25" ht="28.5" spans="1:10">
-      <c r="A25" s="24">
-        <v>19</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="28">
-        <v>1750</v>
-      </c>
-      <c r="I25" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J25" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="32"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="52" t="e">
-        <f>SUM(I7:I25)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J26" s="53"/>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A27" s="37"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="55"/>
+      <c r="J21" s="54"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:G21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
